--- a/results/aggregate_reference_stats/aggregate_control_stats.xlsx
+++ b/results/aggregate_reference_stats/aggregate_control_stats.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I470"/>
+  <dimension ref="A1:I521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -8360,7 +8360,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8379,27 +8379,27 @@
         </is>
       </c>
       <c r="E206">
-        <v>121782.7290187605</v>
+        <v>88877.8698559535</v>
       </c>
       <c r="F206">
-        <v>263990.3741959625</v>
+        <v>203538.478328448</v>
       </c>
       <c r="G206">
         <v>0</v>
       </c>
       <c r="H206">
-        <v>1353335.6</v>
+        <v>1170051.539999996</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>(0, 1353336)</t>
+          <t>(0, 1170052)</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -8418,27 +8418,27 @@
         </is>
       </c>
       <c r="E207">
-        <v>26.65500565901842</v>
+        <v>28.48305616816672</v>
       </c>
       <c r="F207">
-        <v>104.1655912016063</v>
+        <v>115.1475963043827</v>
       </c>
       <c r="G207">
         <v>0</v>
       </c>
       <c r="H207">
-        <v>2446</v>
+        <v>2668.859999999986</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>(0, 2446)</t>
+          <t>(0, 2669)</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -8457,27 +8457,27 @@
         </is>
       </c>
       <c r="E208">
-        <v>114987.9118029975</v>
+        <v>79069.54984482723</v>
       </c>
       <c r="F208">
-        <v>235960.1037231279</v>
+        <v>166012.238597716</v>
       </c>
       <c r="G208">
         <v>0</v>
       </c>
       <c r="H208">
-        <v>1059461.179999999</v>
+        <v>826675.2599999994</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>(0, 1059461)</t>
+          <t>(0, 826675)</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -8496,27 +8496,27 @@
         </is>
       </c>
       <c r="E209">
-        <v>100.6482491339987</v>
+        <v>110.3413498639008</v>
       </c>
       <c r="F209">
-        <v>142.7636600472871</v>
+        <v>187.6842916505585</v>
       </c>
       <c r="G209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209">
-        <v>670</v>
+        <v>1091.859999999986</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>(1, 670)</t>
+          <t>(0, 1092)</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -8535,27 +8535,27 @@
         </is>
       </c>
       <c r="E210">
-        <v>76.89282162088006</v>
+        <v>81.49059227911228</v>
       </c>
       <c r="F210">
-        <v>113.9497573350637</v>
+        <v>139.5275820805502</v>
       </c>
       <c r="G210">
         <v>0</v>
       </c>
       <c r="H210">
-        <v>640</v>
+        <v>787</v>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>(0, 640)</t>
+          <t>(0, 787)</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -8574,27 +8574,27 @@
         </is>
       </c>
       <c r="E211">
-        <v>9.394930891381144</v>
+        <v>10.88265681190519</v>
       </c>
       <c r="F211">
-        <v>18.63507434128904</v>
+        <v>21.01596517398477</v>
       </c>
       <c r="G211">
         <v>0</v>
       </c>
       <c r="H211">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>(0, 116)</t>
+          <t>(0, 109)</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -8613,27 +8613,27 @@
         </is>
       </c>
       <c r="E212">
-        <v>67.11650718523853</v>
+        <v>67.52929606008226</v>
       </c>
       <c r="F212">
-        <v>100.1253883981272</v>
+        <v>115.2565210209357</v>
       </c>
       <c r="G212">
         <v>0</v>
       </c>
       <c r="H212">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>(0, 626)</t>
+          <t>(0, 650)</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -8652,27 +8652,27 @@
         </is>
       </c>
       <c r="E213">
-        <v>3.298864766608362</v>
+        <v>3.621565238123622</v>
       </c>
       <c r="F213">
-        <v>7.094354804542465</v>
+        <v>7.446740430400511</v>
       </c>
       <c r="G213">
         <v>0</v>
       </c>
       <c r="H213">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>(0, 40)</t>
+          <t>(0, 38)</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -8691,27 +8691,27 @@
         </is>
       </c>
       <c r="E214">
-        <v>5.917206845697431</v>
+        <v>6.925314418549204</v>
       </c>
       <c r="F214">
-        <v>11.71374537666169</v>
+        <v>13.26912301582012</v>
       </c>
       <c r="G214">
         <v>0</v>
       </c>
       <c r="H214">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>(0, 76)</t>
+          <t>(0, 69)</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -8730,27 +8730,27 @@
         </is>
       </c>
       <c r="E215">
-        <v>0.2124704187673629</v>
+        <v>0.2189505473763684</v>
       </c>
       <c r="F215">
-        <v>1.810878789951597</v>
+        <v>1.698348123751979</v>
       </c>
       <c r="G215">
         <v>0</v>
       </c>
       <c r="H215">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 153)</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8769,27 +8769,27 @@
         </is>
       </c>
       <c r="E216">
-        <v>0.06879994512466989</v>
+        <v>0.06574476962508195</v>
       </c>
       <c r="F216">
-        <v>0.6237619734502617</v>
+        <v>0.657068893074832</v>
       </c>
       <c r="G216">
         <v>0</v>
       </c>
       <c r="H216">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 90)</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -8808,27 +8808,27 @@
         </is>
       </c>
       <c r="E217">
-        <v>0.06537023699283191</v>
+        <v>0.07015557012576742</v>
       </c>
       <c r="F217">
-        <v>0.7559024685251891</v>
+        <v>0.5535012319649578</v>
       </c>
       <c r="G217">
         <v>0</v>
       </c>
       <c r="H217">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -8847,27 +8847,27 @@
         </is>
       </c>
       <c r="E218">
-        <v>0.0783002366498611</v>
+        <v>0.08305020762551907</v>
       </c>
       <c r="F218">
-        <v>0.6698492795677028</v>
+        <v>0.7595062830563634</v>
       </c>
       <c r="G218">
         <v>0</v>
       </c>
       <c r="H218">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>(0, 42)</t>
+          <t>(0, 71)</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -8886,27 +8886,27 @@
         </is>
       </c>
       <c r="E219">
-        <v>0.04561511815344514</v>
+        <v>0.02751783195247462</v>
       </c>
       <c r="F219">
-        <v>0.6629808105159289</v>
+        <v>0.5757343603611764</v>
       </c>
       <c r="G219">
         <v>0</v>
       </c>
       <c r="H219">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>(0, 48)</t>
+          <t>(0, 97)</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -8925,27 +8925,27 @@
         </is>
       </c>
       <c r="E220">
-        <v>0.014267585828446</v>
+        <v>0.009775287596113727</v>
       </c>
       <c r="F220">
-        <v>0.3112241927582505</v>
+        <v>0.395514050529883</v>
       </c>
       <c r="G220">
         <v>0</v>
       </c>
       <c r="H220">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 81)</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8964,27 +8964,27 @@
         </is>
       </c>
       <c r="E221">
-        <v>0.01594814281304661</v>
+        <v>0.006874490870437702</v>
       </c>
       <c r="F221">
-        <v>0.2463608164028706</v>
+        <v>0.1342885253109043</v>
       </c>
       <c r="G221">
         <v>0</v>
       </c>
       <c r="H221">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="E222">
-        <v>0.01539938951195253</v>
+        <v>0.01086805348592319</v>
       </c>
       <c r="F222">
-        <v>0.2239352387517262</v>
+        <v>0.1813396499440426</v>
       </c>
       <c r="G222">
         <v>0</v>
@@ -9023,7 +9023,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -9042,27 +9042,27 @@
         </is>
       </c>
       <c r="E223">
-        <v>236067.8727499544</v>
+        <v>204889.0743661552</v>
       </c>
       <c r="F223">
-        <v>404134.0545385443</v>
+        <v>332398.8193217463</v>
       </c>
       <c r="G223">
         <v>0</v>
       </c>
       <c r="H223">
-        <v>1353335.6</v>
+        <v>1170051.539999996</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>(0, 1353336)</t>
+          <t>(0, 1170052)</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -9081,27 +9081,27 @@
         </is>
       </c>
       <c r="E224">
-        <v>814.5192412912639</v>
+        <v>783.7538103797659</v>
       </c>
       <c r="F224">
-        <v>1032.60438393415</v>
+        <v>1026.152289869405</v>
       </c>
       <c r="G224">
         <v>0</v>
       </c>
       <c r="H224">
-        <v>2446</v>
+        <v>2668.859999999986</v>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>(0, 2446)</t>
+          <t>(0, 2669)</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -9120,27 +9120,27 @@
         </is>
       </c>
       <c r="E225">
-        <v>110198.5535863578</v>
+        <v>101841.3474022381</v>
       </c>
       <c r="F225">
-        <v>224084.0314931376</v>
+        <v>190751.6015545267</v>
       </c>
       <c r="G225">
         <v>0</v>
       </c>
       <c r="H225">
-        <v>1059461.179999999</v>
+        <v>826675.2599999994</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>(0, 1059461)</t>
+          <t>(0, 826675)</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -9159,27 +9159,27 @@
         </is>
       </c>
       <c r="E226">
-        <v>139.8699616997994</v>
+        <v>121.46914618028</v>
       </c>
       <c r="F226">
-        <v>185.2349820967256</v>
+        <v>193.3656207418846</v>
       </c>
       <c r="G226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H226">
-        <v>1034</v>
+        <v>1091.859999999986</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>(1, 1034)</t>
+          <t>(0, 1092)</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -9198,27 +9198,27 @@
         </is>
       </c>
       <c r="E227">
-        <v>100.7887798650374</v>
+        <v>83.86690457309014</v>
       </c>
       <c r="F227">
-        <v>140.1595769706981</v>
+        <v>138.1418093441035</v>
       </c>
       <c r="G227">
         <v>0</v>
       </c>
       <c r="H227">
-        <v>868.859999999986</v>
+        <v>787</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>(0, 869)</t>
+          <t>(0, 787)</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -9237,27 +9237,27 @@
         </is>
       </c>
       <c r="E228">
-        <v>12.52188582892577</v>
+        <v>10.49414045290334</v>
       </c>
       <c r="F228">
-        <v>22.79681709809547</v>
+        <v>20.47391083391277</v>
       </c>
       <c r="G228">
         <v>0</v>
       </c>
       <c r="H228">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>(0, 116)</t>
+          <t>(0, 109)</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -9276,27 +9276,27 @@
         </is>
       </c>
       <c r="E229">
-        <v>87.42504103592924</v>
+        <v>71.29451934091109</v>
       </c>
       <c r="F229">
-        <v>120.9028439029248</v>
+        <v>116.199345460913</v>
       </c>
       <c r="G229">
         <v>0</v>
       </c>
       <c r="H229">
-        <v>738</v>
+        <v>650</v>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>(0, 738)</t>
+          <t>(0, 650)</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -9315,27 +9315,27 @@
         </is>
       </c>
       <c r="E230">
-        <v>4.054988145175998</v>
+        <v>3.528240373601198</v>
       </c>
       <c r="F230">
-        <v>8.040695864265704</v>
+        <v>7.354894924810538</v>
       </c>
       <c r="G230">
         <v>0</v>
       </c>
       <c r="H230">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>(0, 40)</t>
+          <t>(0, 38)</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9354,27 +9354,27 @@
         </is>
       </c>
       <c r="E231">
-        <v>8.250319168338502</v>
+        <v>6.632214292008107</v>
       </c>
       <c r="F231">
-        <v>14.85948127172184</v>
+        <v>12.75411953420265</v>
       </c>
       <c r="G231">
         <v>0</v>
       </c>
       <c r="H231">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>(0, 76)</t>
+          <t>(0, 69)</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -9393,27 +9393,27 @@
         </is>
       </c>
       <c r="E232">
-        <v>0.2010760532555171</v>
+        <v>0.1944224160719006</v>
       </c>
       <c r="F232">
-        <v>1.42140586984765</v>
+        <v>0.9607674772743632</v>
       </c>
       <c r="G232">
         <v>0</v>
       </c>
       <c r="H232">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>(0, 104)</t>
+          <t>(0, 55)</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -9432,27 +9432,27 @@
         </is>
       </c>
       <c r="E233">
-        <v>0.0583622104687215</v>
+        <v>0.06022557053484889</v>
       </c>
       <c r="F233">
-        <v>0.5832944304896289</v>
+        <v>0.3536497464302016</v>
       </c>
       <c r="G233">
         <v>0</v>
       </c>
       <c r="H233">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 13)</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -9471,27 +9471,27 @@
         </is>
       </c>
       <c r="E234">
-        <v>0.04404523071311326</v>
+        <v>0.05758216582958851</v>
       </c>
       <c r="F234">
-        <v>0.3386793580593879</v>
+        <v>0.3329267246094035</v>
       </c>
       <c r="G234">
         <v>0</v>
       </c>
       <c r="H234">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 12)</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -9510,27 +9510,27 @@
         </is>
       </c>
       <c r="E235">
-        <v>0.0986686120736823</v>
+        <v>0.0766146797074632</v>
       </c>
       <c r="F235">
-        <v>0.7678705764831535</v>
+        <v>0.5139704464004147</v>
       </c>
       <c r="G235">
         <v>0</v>
       </c>
       <c r="H235">
-        <v>68</v>
+        <v>31</v>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 31)</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -9549,27 +9549,27 @@
         </is>
       </c>
       <c r="E236">
-        <v>0.02170344701805581</v>
+        <v>0.02335007489646665</v>
       </c>
       <c r="F236">
-        <v>0.5815866295886996</v>
+        <v>0.3084642869791921</v>
       </c>
       <c r="G236">
         <v>0</v>
       </c>
       <c r="H236">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -9588,27 +9588,27 @@
         </is>
       </c>
       <c r="E237">
-        <v>0.008936713478022979</v>
+        <v>0.004890298704731694</v>
       </c>
       <c r="F237">
-        <v>0.1964398598061775</v>
+        <v>0.08512207200814907</v>
       </c>
       <c r="G237">
         <v>0</v>
       </c>
       <c r="H237">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>(0, 14)</t>
+          <t>(0, 4)</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -9627,10 +9627,10 @@
         </is>
       </c>
       <c r="E238">
-        <v>0.003374065292722962</v>
+        <v>0.005110582430170059</v>
       </c>
       <c r="F238">
-        <v>0.09103707075741298</v>
+        <v>0.09696617779861558</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -9666,27 +9666,27 @@
         </is>
       </c>
       <c r="E239">
-        <v>0.009392668247309867</v>
+        <v>0.01334919376156489</v>
       </c>
       <c r="F239">
-        <v>0.3464407725165749</v>
+        <v>0.1929445923909947</v>
       </c>
       <c r="G239">
         <v>0</v>
       </c>
       <c r="H239">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 13)</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -9705,27 +9705,27 @@
         </is>
       </c>
       <c r="E240">
-        <v>153017.9528593575</v>
+        <v>124935.0843867914</v>
       </c>
       <c r="F240">
-        <v>312845.8747494354</v>
+        <v>256465.1711993142</v>
       </c>
       <c r="G240">
         <v>0</v>
       </c>
       <c r="H240">
-        <v>1353335.6</v>
+        <v>1170051.539999996</v>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>(0, 1353336)</t>
+          <t>(0, 1170052)</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -9744,27 +9744,27 @@
         </is>
       </c>
       <c r="E241">
-        <v>241.9858435311417</v>
+        <v>263.2272753015915</v>
       </c>
       <c r="F241">
-        <v>650.0576973383809</v>
+        <v>677.1983038778335</v>
       </c>
       <c r="G241">
         <v>0</v>
       </c>
       <c r="H241">
-        <v>2446</v>
+        <v>2668.859999999986</v>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>(0, 2446)</t>
+          <t>(0, 2669)</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -9783,27 +9783,27 @@
         </is>
       </c>
       <c r="E242">
-        <v>113678.9343535628</v>
+        <v>86147.20750080103</v>
       </c>
       <c r="F242">
-        <v>232781.4555733207</v>
+        <v>174395.8368114562</v>
       </c>
       <c r="G242">
         <v>0</v>
       </c>
       <c r="H242">
-        <v>1059461.179999999</v>
+        <v>826675.2599999994</v>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>(0, 1059461)</t>
+          <t>(0, 826675)</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9822,27 +9822,27 @@
         </is>
       </c>
       <c r="E243">
-        <v>111.3679186501508</v>
+        <v>113.7999583727011</v>
       </c>
       <c r="F243">
-        <v>156.5042851370532</v>
+        <v>189.5370006221188</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243">
-        <v>1034</v>
+        <v>1091.859999999986</v>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>(1, 1034)</t>
+          <t>(0, 1092)</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -9861,27 +9861,27 @@
         </is>
       </c>
       <c r="E244">
-        <v>83.42381576651795</v>
+        <v>82.22916923413986</v>
       </c>
       <c r="F244">
-        <v>122.1384529276929</v>
+        <v>139.1017542348649</v>
       </c>
       <c r="G244">
         <v>0</v>
       </c>
       <c r="H244">
-        <v>868.859999999986</v>
+        <v>787</v>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>(0, 869)</t>
+          <t>(0, 787)</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9900,27 +9900,27 @@
         </is>
       </c>
       <c r="E245">
-        <v>10.24955761034818</v>
+        <v>10.76190280573471</v>
       </c>
       <c r="F245">
-        <v>19.90785574075209</v>
+        <v>20.84963524593703</v>
       </c>
       <c r="G245">
         <v>0</v>
       </c>
       <c r="H245">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>(0, 116)</t>
+          <t>(0, 109)</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -9939,27 +9939,27 @@
         </is>
       </c>
       <c r="E246">
-        <v>72.66702390150287</v>
+        <v>68.69955770995084</v>
       </c>
       <c r="F246">
-        <v>106.5918621167726</v>
+        <v>115.5627263799805</v>
       </c>
       <c r="G246">
         <v>0</v>
       </c>
       <c r="H246">
-        <v>738</v>
+        <v>650</v>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>(0, 738)</t>
+          <t>(0, 650)</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -9978,27 +9978,27 @@
         </is>
       </c>
       <c r="E247">
-        <v>3.505520524387508</v>
+        <v>3.59255912034945</v>
       </c>
       <c r="F247">
-        <v>7.372686135493365</v>
+        <v>7.418391331164465</v>
       </c>
       <c r="G247">
         <v>0</v>
       </c>
       <c r="H247">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>(0, 40)</t>
+          <t>(0, 38)</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -10017,27 +10017,27 @@
         </is>
       </c>
       <c r="E248">
-        <v>6.554868778506093</v>
+        <v>6.834216544112613</v>
       </c>
       <c r="F248">
-        <v>12.69388192252083</v>
+        <v>13.11183721805535</v>
       </c>
       <c r="G248">
         <v>0</v>
       </c>
       <c r="H248">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>(0, 76)</t>
+          <t>(0, 69)</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -10056,27 +10056,27 @@
         </is>
       </c>
       <c r="E249">
-        <v>0.2093562295939984</v>
+        <v>0.2113270070793794</v>
       </c>
       <c r="F249">
-        <v>1.713237544530557</v>
+        <v>1.508278039417058</v>
       </c>
       <c r="G249">
         <v>0</v>
       </c>
       <c r="H249">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 153)</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -10095,27 +10095,27 @@
         </is>
       </c>
       <c r="E250">
-        <v>0.06594721232210951</v>
+        <v>0.06402935820016706</v>
       </c>
       <c r="F250">
-        <v>0.6129776342458438</v>
+        <v>0.5800233670550237</v>
       </c>
       <c r="G250">
         <v>0</v>
       </c>
       <c r="H250">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 90)</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -10134,27 +10134,27 @@
         </is>
       </c>
       <c r="E251">
-        <v>0.0595419086309598</v>
+        <v>0.06624765504114803</v>
       </c>
       <c r="F251">
-        <v>0.668323691790244</v>
+        <v>0.4956055704717157</v>
       </c>
       <c r="G251">
         <v>0</v>
       </c>
       <c r="H251">
-        <v>98</v>
+        <v>54</v>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -10173,27 +10173,27 @@
         </is>
       </c>
       <c r="E252">
-        <v>0.08386710864092914</v>
+        <v>0.08104999383806433</v>
       </c>
       <c r="F252">
-        <v>0.698056920972483</v>
+        <v>0.6925813770047471</v>
       </c>
       <c r="G252">
         <v>0</v>
       </c>
       <c r="H252">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 71)</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -10212,27 +10212,27 @@
         </is>
       </c>
       <c r="E253">
-        <v>0.03907982952421304</v>
+        <v>0.02622245957085541</v>
       </c>
       <c r="F253">
-        <v>0.6418423387715552</v>
+        <v>0.5079580312698015</v>
       </c>
       <c r="G253">
         <v>0</v>
       </c>
       <c r="H253">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 97)</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -10251,27 +10251,27 @@
         </is>
       </c>
       <c r="E254">
-        <v>0.01281060738229943</v>
+        <v>0.008256993796984758</v>
       </c>
       <c r="F254">
-        <v>0.2844969616805438</v>
+        <v>0.3317644637818284</v>
       </c>
       <c r="G254">
         <v>0</v>
       </c>
       <c r="H254">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 81)</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -10290,27 +10290,27 @@
         </is>
       </c>
       <c r="E255">
-        <v>0.012511527054308</v>
+        <v>0.006326253953908722</v>
       </c>
       <c r="F255">
-        <v>0.2154099716702751</v>
+        <v>0.1239005032385335</v>
       </c>
       <c r="G255">
         <v>0</v>
       </c>
       <c r="H255">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>extensive_baseline</t>
+          <t>ads_intensive_aggregate</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -10329,27 +10329,27 @@
         </is>
       </c>
       <c r="E256">
-        <v>0.01375769508760561</v>
+        <v>0.01163921181996194</v>
       </c>
       <c r="F256">
-        <v>0.263151922959706</v>
+        <v>0.1850267693554523</v>
       </c>
       <c r="G256">
         <v>0</v>
       </c>
       <c r="H256">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 14)</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -10368,10 +10368,10 @@
         </is>
       </c>
       <c r="E257">
-        <v>117754.2984211805</v>
+        <v>121782.7290187605</v>
       </c>
       <c r="F257">
-        <v>253840.2038892482</v>
+        <v>263990.3741959625</v>
       </c>
       <c r="G257">
         <v>0</v>
@@ -10388,7 +10388,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -10407,10 +10407,10 @@
         </is>
       </c>
       <c r="E258">
-        <v>48.89652659703668</v>
+        <v>26.65500565901842</v>
       </c>
       <c r="F258">
-        <v>137.3125083754152</v>
+        <v>104.1655912016063</v>
       </c>
       <c r="G258">
         <v>0</v>
@@ -10427,7 +10427,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -10446,10 +10446,10 @@
         </is>
       </c>
       <c r="E259">
-        <v>111630.140568375</v>
+        <v>114987.9118029975</v>
       </c>
       <c r="F259">
-        <v>228604.3669843768</v>
+        <v>235960.1037231279</v>
       </c>
       <c r="G259">
         <v>0</v>
@@ -10466,7 +10466,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -10485,27 +10485,27 @@
         </is>
       </c>
       <c r="E260">
-        <v>152.5997085256255</v>
+        <v>100.6482491339987</v>
       </c>
       <c r="F260">
-        <v>166.9144482130496</v>
+        <v>142.7636600472871</v>
       </c>
       <c r="G260">
         <v>1</v>
       </c>
       <c r="H260">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>(1, 668)</t>
+          <t>(1, 670)</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -10524,27 +10524,27 @@
         </is>
       </c>
       <c r="E261">
-        <v>115.9485061938305</v>
+        <v>76.89282162088006</v>
       </c>
       <c r="F261">
-        <v>133.8432708703262</v>
+        <v>113.9497573350637</v>
       </c>
       <c r="G261">
         <v>0</v>
       </c>
       <c r="H261">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>(0, 625)</t>
+          <t>(0, 640)</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -10563,10 +10563,10 @@
         </is>
       </c>
       <c r="E262">
-        <v>12.348797668205</v>
+        <v>9.394930891381144</v>
       </c>
       <c r="F262">
-        <v>20.30183515900078</v>
+        <v>18.63507434128904</v>
       </c>
       <c r="G262">
         <v>0</v>
@@ -10583,7 +10583,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -10602,27 +10602,27 @@
         </is>
       </c>
       <c r="E263">
-        <v>102.975710468788</v>
+        <v>67.11650718523853</v>
       </c>
       <c r="F263">
-        <v>118.997214742138</v>
+        <v>100.1253883981272</v>
       </c>
       <c r="G263">
         <v>0</v>
       </c>
       <c r="H263">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>(0, 617)</t>
+          <t>(0, 626)</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -10641,10 +10641,10 @@
         </is>
       </c>
       <c r="E264">
-        <v>4.24969638085985</v>
+        <v>3.298864766608362</v>
       </c>
       <c r="F264">
-        <v>7.692607991854584</v>
+        <v>7.094354804542465</v>
       </c>
       <c r="G264">
         <v>0</v>
@@ -10661,7 +10661,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -10680,10 +10680,10 @@
         </is>
       </c>
       <c r="E265">
-        <v>7.881224192373087</v>
+        <v>5.917206845697431</v>
       </c>
       <c r="F265">
-        <v>12.84664082261146</v>
+        <v>11.71374537666169</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -10700,7 +10700,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -10719,27 +10719,27 @@
         </is>
       </c>
       <c r="E266">
-        <v>0.2562545542871023</v>
+        <v>0.2124704187673629</v>
       </c>
       <c r="F266">
-        <v>1.443346337662553</v>
+        <v>1.810878789951597</v>
       </c>
       <c r="G266">
         <v>0</v>
       </c>
       <c r="H266">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>(0, 45)</t>
+          <t>(0, 173)</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -10758,27 +10758,27 @@
         </is>
       </c>
       <c r="E267">
-        <v>0.0782122905027933</v>
+        <v>0.06879994512466989</v>
       </c>
       <c r="F267">
-        <v>0.5698992380331057</v>
+        <v>0.6237619734502617</v>
       </c>
       <c r="G267">
         <v>0</v>
       </c>
       <c r="H267">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -10797,27 +10797,27 @@
         </is>
       </c>
       <c r="E268">
-        <v>0.0782122905027933</v>
+        <v>0.06537023699283191</v>
       </c>
       <c r="F268">
-        <v>0.5392323581430714</v>
+        <v>0.7559024685251891</v>
       </c>
       <c r="G268">
         <v>0</v>
       </c>
       <c r="H268">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 98)</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -10836,27 +10836,27 @@
         </is>
       </c>
       <c r="E269">
-        <v>0.09982997328151566</v>
+        <v>0.0783002366498611</v>
       </c>
       <c r="F269">
-        <v>0.6242526884937428</v>
+        <v>0.6698492795677028</v>
       </c>
       <c r="G269">
         <v>0</v>
       </c>
       <c r="H269">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 42)</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -10875,27 +10875,27 @@
         </is>
       </c>
       <c r="E270">
-        <v>0.05027932960893855</v>
+        <v>0.04561511815344514</v>
       </c>
       <c r="F270">
-        <v>0.7288635166754226</v>
+        <v>0.6629808105159289</v>
       </c>
       <c r="G270">
         <v>0</v>
       </c>
       <c r="H270">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 48)</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -10914,27 +10914,27 @@
         </is>
       </c>
       <c r="E271">
-        <v>0.01433082341510809</v>
+        <v>0.014267585828446</v>
       </c>
       <c r="F271">
-        <v>0.3232768032214736</v>
+        <v>0.3112241927582505</v>
       </c>
       <c r="G271">
         <v>0</v>
       </c>
       <c r="H271">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 33)</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -10953,27 +10953,27 @@
         </is>
       </c>
       <c r="E272">
-        <v>0.02113189215448142</v>
+        <v>0.01594814281304661</v>
       </c>
       <c r="F272">
-        <v>0.3397683732619002</v>
+        <v>0.2463608164028706</v>
       </c>
       <c r="G272">
         <v>0</v>
       </c>
       <c r="H272">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>(0, 17)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -10992,27 +10992,27 @@
         </is>
       </c>
       <c r="E273">
-        <v>0.01481661403934904</v>
+        <v>0.01539938951195253</v>
       </c>
       <c r="F273">
-        <v>0.2237676469055614</v>
+        <v>0.2239352387517262</v>
       </c>
       <c r="G273">
         <v>0</v>
       </c>
       <c r="H273">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>(0, 10)</t>
+          <t>(0, 14)</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -11031,10 +11031,10 @@
         </is>
       </c>
       <c r="E274">
-        <v>233235.6326587578</v>
+        <v>236067.8727499544</v>
       </c>
       <c r="F274">
-        <v>398882.689327079</v>
+        <v>404134.0545385443</v>
       </c>
       <c r="G274">
         <v>0</v>
@@ -11051,7 +11051,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -11070,10 +11070,10 @@
         </is>
       </c>
       <c r="E275">
-        <v>838.2393579902302</v>
+        <v>814.5192412912639</v>
       </c>
       <c r="F275">
-        <v>1032.418096667703</v>
+        <v>1032.60438393415</v>
       </c>
       <c r="G275">
         <v>0</v>
@@ -11090,7 +11090,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -11109,10 +11109,10 @@
         </is>
       </c>
       <c r="E276">
-        <v>108936.6405024424</v>
+        <v>110198.5535863578</v>
       </c>
       <c r="F276">
-        <v>224815.5313221877</v>
+        <v>224084.0314931376</v>
       </c>
       <c r="G276">
         <v>0</v>
@@ -11129,7 +11129,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -11148,27 +11148,27 @@
         </is>
       </c>
       <c r="E277">
-        <v>188.3977669225401</v>
+        <v>139.8699616997994</v>
       </c>
       <c r="F277">
-        <v>202.257108749489</v>
+        <v>185.2349820967256</v>
       </c>
       <c r="G277">
         <v>1</v>
       </c>
       <c r="H277">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>(1, 1031)</t>
+          <t>(1, 1034)</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -11187,10 +11187,10 @@
         </is>
       </c>
       <c r="E278">
-        <v>135.1303000697837</v>
+        <v>100.7887798650374</v>
       </c>
       <c r="F278">
-        <v>150.5154265316417</v>
+        <v>140.1595769706981</v>
       </c>
       <c r="G278">
         <v>0</v>
@@ -11207,7 +11207,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -11226,10 +11226,10 @@
         </is>
       </c>
       <c r="E279">
-        <v>15.10607117934403</v>
+        <v>12.52188582892577</v>
       </c>
       <c r="F279">
-        <v>22.96852165155734</v>
+        <v>22.79681709809547</v>
       </c>
       <c r="G279">
         <v>0</v>
@@ -11246,7 +11246,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -11265,10 +11265,10 @@
         </is>
       </c>
       <c r="E280">
-        <v>119.3545010467551</v>
+        <v>87.42504103592924</v>
       </c>
       <c r="F280">
-        <v>132.0678943215289</v>
+        <v>120.9028439029248</v>
       </c>
       <c r="G280">
         <v>0</v>
@@ -11285,7 +11285,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -11304,10 +11304,10 @@
         </is>
       </c>
       <c r="E281">
-        <v>4.465457083042568</v>
+        <v>4.054988145175998</v>
       </c>
       <c r="F281">
-        <v>7.729114050027431</v>
+        <v>8.040695864265704</v>
       </c>
       <c r="G281">
         <v>0</v>
@@ -11324,7 +11324,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -11343,10 +11343,10 @@
         </is>
       </c>
       <c r="E282">
-        <v>10.42986741102582</v>
+        <v>8.250319168338502</v>
       </c>
       <c r="F282">
-        <v>15.36945389079919</v>
+        <v>14.85948127172184</v>
       </c>
       <c r="G282">
         <v>0</v>
@@ -11363,7 +11363,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -11382,27 +11382,27 @@
         </is>
       </c>
       <c r="E283">
-        <v>0.2372644801116539</v>
+        <v>0.2010760532555171</v>
       </c>
       <c r="F283">
-        <v>0.6091309845986091</v>
+        <v>1.42140586984765</v>
       </c>
       <c r="G283">
         <v>0</v>
       </c>
       <c r="H283">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>(0, 6)</t>
+          <t>(0, 104)</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -11421,27 +11421,27 @@
         </is>
       </c>
       <c r="E284">
-        <v>0.052337752965806</v>
+        <v>0.0583622104687215</v>
       </c>
       <c r="F284">
-        <v>0.2521896684244442</v>
+        <v>0.5832944304896289</v>
       </c>
       <c r="G284">
         <v>0</v>
       </c>
       <c r="H284">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -11460,27 +11460,27 @@
         </is>
       </c>
       <c r="E285">
-        <v>0.05722260990928123</v>
+        <v>0.04404523071311326</v>
       </c>
       <c r="F285">
-        <v>0.268593150913208</v>
+        <v>0.3386793580593879</v>
       </c>
       <c r="G285">
         <v>0</v>
       </c>
       <c r="H285">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -11499,27 +11499,27 @@
         </is>
       </c>
       <c r="E286">
-        <v>0.1277041172365666</v>
+        <v>0.0986686120736823</v>
       </c>
       <c r="F286">
-        <v>0.3916286600394836</v>
+        <v>0.7678705764831535</v>
       </c>
       <c r="G286">
         <v>0</v>
       </c>
       <c r="H286">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 68)</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -11538,27 +11538,27 @@
         </is>
       </c>
       <c r="E287">
-        <v>0.01535240753663643</v>
+        <v>0.02170344701805581</v>
       </c>
       <c r="F287">
-        <v>0.1338677092183344</v>
+        <v>0.5815866295886996</v>
       </c>
       <c r="G287">
         <v>0</v>
       </c>
       <c r="H287">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>(0, 2)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -11577,27 +11577,27 @@
         </is>
       </c>
       <c r="E288">
-        <v>0.00418702023726448</v>
+        <v>0.008936713478022979</v>
       </c>
       <c r="F288">
-        <v>0.06459412320943615</v>
+        <v>0.1964398598061775</v>
       </c>
       <c r="G288">
         <v>0</v>
       </c>
       <c r="H288">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 14)</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11616,27 +11616,27 @@
         </is>
       </c>
       <c r="E289">
-        <v>0.00418702023726448</v>
+        <v>0.003374065292722962</v>
       </c>
       <c r="F289">
-        <v>0.06459412320943615</v>
+        <v>0.09103707075741298</v>
       </c>
       <c r="G289">
         <v>0</v>
       </c>
       <c r="H289">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 6)</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -11655,27 +11655,27 @@
         </is>
       </c>
       <c r="E290">
-        <v>0.006978367062107467</v>
+        <v>0.009392668247309867</v>
       </c>
       <c r="F290">
-        <v>0.08327369698711283</v>
+        <v>0.3464407725165749</v>
       </c>
       <c r="G290">
         <v>0</v>
       </c>
       <c r="H290">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 34)</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -11694,10 +11694,10 @@
         </is>
       </c>
       <c r="E291">
-        <v>147571.3708468468</v>
+        <v>153017.9528593575</v>
       </c>
       <c r="F291">
-        <v>302340.1742073931</v>
+        <v>312845.8747494354</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -11714,7 +11714,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -11733,10 +11733,10 @@
         </is>
       </c>
       <c r="E292">
-        <v>252.7034234234234</v>
+        <v>241.9858435311417</v>
       </c>
       <c r="F292">
-        <v>639.0704224387156</v>
+        <v>650.0576973383809</v>
       </c>
       <c r="G292">
         <v>0</v>
@@ -11753,7 +11753,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -11772,10 +11772,10 @@
         </is>
       </c>
       <c r="E293">
-        <v>110934.6837045045</v>
+        <v>113678.9343535628</v>
       </c>
       <c r="F293">
-        <v>227615.0057220722</v>
+        <v>232781.4555733207</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -11792,7 +11792,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11811,27 +11811,27 @@
         </is>
       </c>
       <c r="E294">
-        <v>161.8427027027027</v>
+        <v>111.3679186501508</v>
       </c>
       <c r="F294">
-        <v>177.3922287633733</v>
+        <v>156.5042851370532</v>
       </c>
       <c r="G294">
         <v>1</v>
       </c>
       <c r="H294">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>(1, 1031)</t>
+          <t>(1, 1034)</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -11850,10 +11850,10 @@
         </is>
       </c>
       <c r="E295">
-        <v>120.9012108108108</v>
+        <v>83.42381576651795</v>
       </c>
       <c r="F295">
-        <v>138.5811277168841</v>
+        <v>122.1384529276929</v>
       </c>
       <c r="G295">
         <v>0</v>
@@ -11870,7 +11870,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -11889,10 +11889,10 @@
         </is>
       </c>
       <c r="E296">
-        <v>13.06072072072072</v>
+        <v>10.24955761034818</v>
       </c>
       <c r="F296">
-        <v>21.05526773409256</v>
+        <v>19.90785574075209</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -11909,7 +11909,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="E297">
-        <v>107.2046846846847</v>
+        <v>72.66702390150287</v>
       </c>
       <c r="F297">
-        <v>122.7030484994025</v>
+        <v>106.5918621167726</v>
       </c>
       <c r="G297">
         <v>0</v>
@@ -11948,7 +11948,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -11967,10 +11967,10 @@
         </is>
       </c>
       <c r="E298">
-        <v>4.305405405405406</v>
+        <v>3.505520524387508</v>
       </c>
       <c r="F298">
-        <v>7.701932103400988</v>
+        <v>7.372686135493365</v>
       </c>
       <c r="G298">
         <v>0</v>
@@ -11987,7 +11987,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12006,10 +12006,10 @@
         </is>
       </c>
       <c r="E299">
-        <v>8.539279279279279</v>
+        <v>6.554868778506093</v>
       </c>
       <c r="F299">
-        <v>13.58752447100487</v>
+        <v>12.69388192252083</v>
       </c>
       <c r="G299">
         <v>0</v>
@@ -12026,7 +12026,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -12045,27 +12045,27 @@
         </is>
       </c>
       <c r="E300">
-        <v>0.2513513513513513</v>
+        <v>0.2093562295939984</v>
       </c>
       <c r="F300">
-        <v>1.281047287423756</v>
+        <v>1.713237544530557</v>
       </c>
       <c r="G300">
         <v>0</v>
       </c>
       <c r="H300">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>(0, 45)</t>
+          <t>(0, 173)</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12084,27 +12084,27 @@
         </is>
       </c>
       <c r="E301">
-        <v>0.07153153153153154</v>
+        <v>0.06594721232210951</v>
       </c>
       <c r="F301">
-        <v>0.5073974283479409</v>
+        <v>0.6129776342458438</v>
       </c>
       <c r="G301">
         <v>0</v>
       </c>
       <c r="H301">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -12123,27 +12123,27 @@
         </is>
       </c>
       <c r="E302">
-        <v>0.0727927927927928</v>
+        <v>0.0595419086309598</v>
       </c>
       <c r="F302">
-        <v>0.4841312633394754</v>
+        <v>0.668323691790244</v>
       </c>
       <c r="G302">
         <v>0</v>
       </c>
       <c r="H302">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 98)</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12162,27 +12162,27 @@
         </is>
       </c>
       <c r="E303">
-        <v>0.107027027027027</v>
+        <v>0.08386710864092914</v>
       </c>
       <c r="F303">
-        <v>0.5733974504136869</v>
+        <v>0.698056920972483</v>
       </c>
       <c r="G303">
         <v>0</v>
       </c>
       <c r="H303">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 68)</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -12201,27 +12201,27 @@
         </is>
       </c>
       <c r="E304">
-        <v>0.04126126126126126</v>
+        <v>0.03907982952421304</v>
       </c>
       <c r="F304">
-        <v>0.6315931637705925</v>
+        <v>0.6418423387715552</v>
       </c>
       <c r="G304">
         <v>0</v>
       </c>
       <c r="H304">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -12240,27 +12240,27 @@
         </is>
       </c>
       <c r="E305">
-        <v>0.01171171171171171</v>
+        <v>0.01281060738229943</v>
       </c>
       <c r="F305">
-        <v>0.2803849845224184</v>
+        <v>0.2844969616805438</v>
       </c>
       <c r="G305">
         <v>0</v>
       </c>
       <c r="H305">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 33)</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -12279,27 +12279,27 @@
         </is>
       </c>
       <c r="E306">
-        <v>0.01675675675675676</v>
+        <v>0.012511527054308</v>
       </c>
       <c r="F306">
-        <v>0.2945536808453654</v>
+        <v>0.2154099716702751</v>
       </c>
       <c r="G306">
         <v>0</v>
       </c>
       <c r="H306">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>(0, 17)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>extensive_baseline_strong</t>
+          <t>extensive_baseline</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -12318,27 +12318,27 @@
         </is>
       </c>
       <c r="E307">
-        <v>0.01279279279279279</v>
+        <v>0.01375769508760561</v>
       </c>
       <c r="F307">
-        <v>0.1973384407842458</v>
+        <v>0.263151922959706</v>
       </c>
       <c r="G307">
         <v>0</v>
       </c>
       <c r="H307">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>(0, 10)</t>
+          <t>(0, 34)</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -12357,10 +12357,10 @@
         </is>
       </c>
       <c r="E308">
-        <v>122025.6116065035</v>
+        <v>117754.2984211805</v>
       </c>
       <c r="F308">
-        <v>263020.7700876168</v>
+        <v>253840.2038892482</v>
       </c>
       <c r="G308">
         <v>0</v>
@@ -12377,7 +12377,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -12396,10 +12396,10 @@
         </is>
       </c>
       <c r="E309">
-        <v>26.62902156327083</v>
+        <v>48.89652659703668</v>
       </c>
       <c r="F309">
-        <v>104.4420895756076</v>
+        <v>137.3125083754152</v>
       </c>
       <c r="G309">
         <v>0</v>
@@ -12416,7 +12416,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -12435,10 +12435,10 @@
         </is>
       </c>
       <c r="E310">
-        <v>115348.880936265</v>
+        <v>111630.140568375</v>
       </c>
       <c r="F310">
-        <v>235396.665709708</v>
+        <v>228604.3669843768</v>
       </c>
       <c r="G310">
         <v>0</v>
@@ -12455,7 +12455,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -12474,27 +12474,27 @@
         </is>
       </c>
       <c r="E311">
-        <v>100.1684481341007</v>
+        <v>152.5997085256255</v>
       </c>
       <c r="F311">
-        <v>141.9602120241412</v>
+        <v>166.9144482130496</v>
       </c>
       <c r="G311">
         <v>1</v>
       </c>
       <c r="H311">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>(1, 670)</t>
+          <t>(1, 668)</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -12513,27 +12513,27 @@
         </is>
       </c>
       <c r="E312">
-        <v>77.06028697981593</v>
+        <v>115.9485061938305</v>
       </c>
       <c r="F312">
-        <v>113.5625546613916</v>
+        <v>133.8432708703262</v>
       </c>
       <c r="G312">
         <v>0</v>
       </c>
       <c r="H312">
-        <v>653</v>
+        <v>625</v>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>(0, 653)</t>
+          <t>(0, 625)</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -12552,10 +12552,10 @@
         </is>
       </c>
       <c r="E313">
-        <v>9.73323077739172</v>
+        <v>12.348797668205</v>
       </c>
       <c r="F313">
-        <v>18.99030715458966</v>
+        <v>20.30183515900078</v>
       </c>
       <c r="G313">
         <v>0</v>
@@ -12572,7 +12572,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -12591,27 +12591,27 @@
         </is>
       </c>
       <c r="E314">
-        <v>66.8974352173567</v>
+        <v>102.975710468788</v>
       </c>
       <c r="F314">
-        <v>99.25385502892921</v>
+        <v>118.997214742138</v>
       </c>
       <c r="G314">
         <v>0</v>
       </c>
       <c r="H314">
-        <v>631</v>
+        <v>617</v>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>(0, 631)</t>
+          <t>(0, 617)</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12630,10 +12630,10 @@
         </is>
       </c>
       <c r="E315">
-        <v>3.404901466726786</v>
+        <v>4.24969638085985</v>
       </c>
       <c r="F315">
-        <v>7.192508831064703</v>
+        <v>7.692607991854584</v>
       </c>
       <c r="G315">
         <v>0</v>
@@ -12650,7 +12650,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12669,10 +12669,10 @@
         </is>
       </c>
       <c r="E316">
-        <v>6.152826035063523</v>
+        <v>7.881224192373087</v>
       </c>
       <c r="F316">
-        <v>12.00801570426784</v>
+        <v>12.84664082261146</v>
       </c>
       <c r="G316">
         <v>0</v>
@@ -12689,7 +12689,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12708,27 +12708,27 @@
         </is>
       </c>
       <c r="E317">
-        <v>0.2046521496963107</v>
+        <v>0.2562545542871023</v>
       </c>
       <c r="F317">
-        <v>1.685758890151864</v>
+        <v>1.443346337662553</v>
       </c>
       <c r="G317">
         <v>0</v>
       </c>
       <c r="H317">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 45)</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12747,27 +12747,27 @@
         </is>
       </c>
       <c r="E318">
-        <v>0.06514070498368831</v>
+        <v>0.0782122905027933</v>
       </c>
       <c r="F318">
-        <v>0.5846246354430156</v>
+        <v>0.5698992380331057</v>
       </c>
       <c r="G318">
         <v>0</v>
       </c>
       <c r="H318">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12786,27 +12786,27 @@
         </is>
       </c>
       <c r="E319">
-        <v>0.06285971938572528</v>
+        <v>0.0782122905027933</v>
       </c>
       <c r="F319">
-        <v>0.6922087080290286</v>
+        <v>0.5392323581430714</v>
       </c>
       <c r="G319">
         <v>0</v>
       </c>
       <c r="H319">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12825,27 +12825,27 @@
         </is>
       </c>
       <c r="E320">
-        <v>0.07665172532689707</v>
+        <v>0.09982997328151566</v>
       </c>
       <c r="F320">
-        <v>0.6438784865424627</v>
+        <v>0.6242526884937428</v>
       </c>
       <c r="G320">
         <v>0</v>
       </c>
       <c r="H320">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>(0, 42)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12864,27 +12864,27 @@
         </is>
       </c>
       <c r="E321">
-        <v>0.04373657268652362</v>
+        <v>0.05027932960893855</v>
       </c>
       <c r="F321">
-        <v>0.622140232443614</v>
+        <v>0.7288635166754226</v>
       </c>
       <c r="G321">
         <v>0</v>
       </c>
       <c r="H321">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>(0, 48)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -12903,27 +12903,27 @@
         </is>
       </c>
       <c r="E322">
-        <v>0.01307588255576479</v>
+        <v>0.01433082341510809</v>
       </c>
       <c r="F322">
-        <v>0.2819219105705569</v>
+        <v>0.3232768032214736</v>
       </c>
       <c r="G322">
         <v>0</v>
       </c>
       <c r="H322">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -12942,27 +12942,27 @@
         </is>
       </c>
       <c r="E323">
-        <v>0.01506511418189534</v>
+        <v>0.02113189215448142</v>
       </c>
       <c r="F323">
-        <v>0.2351889802489741</v>
+        <v>0.3397683732619002</v>
       </c>
       <c r="G323">
         <v>0</v>
       </c>
       <c r="H323">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 17)</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -12981,27 +12981,27 @@
         </is>
       </c>
       <c r="E324">
-        <v>0.01559557594886348</v>
+        <v>0.01481661403934904</v>
       </c>
       <c r="F324">
-        <v>0.2208455090834819</v>
+        <v>0.2237676469055614</v>
       </c>
       <c r="G324">
         <v>0</v>
       </c>
       <c r="H324">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>(0, 14)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -13020,10 +13020,10 @@
         </is>
       </c>
       <c r="E325">
-        <v>238583.1102798026</v>
+        <v>233235.6326587578</v>
       </c>
       <c r="F325">
-        <v>405571.4550739584</v>
+        <v>398882.689327079</v>
       </c>
       <c r="G325">
         <v>0</v>
@@ -13040,7 +13040,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13059,10 +13059,10 @@
         </is>
       </c>
       <c r="E326">
-        <v>815.1281235078784</v>
+        <v>838.2393579902302</v>
       </c>
       <c r="F326">
-        <v>1031.828072407631</v>
+        <v>1032.418096667703</v>
       </c>
       <c r="G326">
         <v>0</v>
@@ -13079,7 +13079,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13098,10 +13098,10 @@
         </is>
       </c>
       <c r="E327">
-        <v>112181.1115222028</v>
+        <v>108936.6405024424</v>
       </c>
       <c r="F327">
-        <v>224457.0875408288</v>
+        <v>224815.5313221877</v>
       </c>
       <c r="G327">
         <v>0</v>
@@ -13118,7 +13118,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -13137,27 +13137,27 @@
         </is>
       </c>
       <c r="E328">
-        <v>146.5346968008913</v>
+        <v>188.3977669225401</v>
       </c>
       <c r="F328">
-        <v>190.85408354944</v>
+        <v>202.257108749489</v>
       </c>
       <c r="G328">
         <v>1</v>
       </c>
       <c r="H328">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>(1, 1034)</t>
+          <t>(1, 1031)</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13176,10 +13176,10 @@
         </is>
       </c>
       <c r="E329">
-        <v>104.4204249562311</v>
+        <v>135.1303000697837</v>
       </c>
       <c r="F329">
-        <v>143.1890819091348</v>
+        <v>150.5154265316417</v>
       </c>
       <c r="G329">
         <v>0</v>
@@ -13196,7 +13196,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -13215,10 +13215,10 @@
         </is>
       </c>
       <c r="E330">
-        <v>12.66512812350788</v>
+        <v>15.10607117934403</v>
       </c>
       <c r="F330">
-        <v>22.98141407071184</v>
+        <v>22.96852165155734</v>
       </c>
       <c r="G330">
         <v>0</v>
@@ -13235,7 +13235,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13254,10 +13254,10 @@
         </is>
       </c>
       <c r="E331">
-        <v>90.89559127805188</v>
+        <v>119.3545010467551</v>
       </c>
       <c r="F331">
-        <v>124.0372038381766</v>
+        <v>132.0678943215289</v>
       </c>
       <c r="G331">
         <v>0</v>
@@ -13274,7 +13274,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -13293,10 +13293,10 @@
         </is>
       </c>
       <c r="E332">
-        <v>4.122075441667993</v>
+        <v>4.465457083042568</v>
       </c>
       <c r="F332">
-        <v>8.147900333619466</v>
+        <v>7.729114050027431</v>
       </c>
       <c r="G332">
         <v>0</v>
@@ -13313,7 +13313,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -13332,10 +13332,10 @@
         </is>
       </c>
       <c r="E333">
-        <v>8.298663059048225</v>
+        <v>10.42986741102582</v>
       </c>
       <c r="F333">
-        <v>14.88767899561893</v>
+        <v>15.36945389079919</v>
       </c>
       <c r="G333">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -13371,27 +13371,27 @@
         </is>
       </c>
       <c r="E334">
-        <v>0.1956867738341557</v>
+        <v>0.2372644801116539</v>
       </c>
       <c r="F334">
-        <v>1.344094575787843</v>
+        <v>0.6091309845986091</v>
       </c>
       <c r="G334">
         <v>0</v>
       </c>
       <c r="H334">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>(0, 104)</t>
+          <t>(0, 6)</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -13410,27 +13410,27 @@
         </is>
       </c>
       <c r="E335">
-        <v>0.05634251153907369</v>
+        <v>0.052337752965806</v>
       </c>
       <c r="F335">
-        <v>0.5510984221513963</v>
+        <v>0.2521896684244442</v>
       </c>
       <c r="G335">
         <v>0</v>
       </c>
       <c r="H335">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -13449,27 +13449,27 @@
         </is>
       </c>
       <c r="E336">
-        <v>0.04321184147700143</v>
+        <v>0.05722260990928123</v>
       </c>
       <c r="F336">
-        <v>0.3250438116820141</v>
+        <v>0.268593150913208</v>
       </c>
       <c r="G336">
         <v>0</v>
       </c>
       <c r="H336">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -13488,27 +13488,27 @@
         </is>
       </c>
       <c r="E337">
-        <v>0.09613242081808053</v>
+        <v>0.1277041172365666</v>
       </c>
       <c r="F337">
-        <v>0.7297810254164189</v>
+        <v>0.3916286600394836</v>
       </c>
       <c r="G337">
         <v>0</v>
       </c>
       <c r="H337">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -13527,27 +13527,27 @@
         </is>
       </c>
       <c r="E338">
-        <v>0.02029285373229349</v>
+        <v>0.01535240753663643</v>
       </c>
       <c r="F338">
-        <v>0.5446863985501021</v>
+        <v>0.1338677092183344</v>
       </c>
       <c r="G338">
         <v>0</v>
       </c>
       <c r="H338">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 2)</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -13566,27 +13566,27 @@
         </is>
       </c>
       <c r="E339">
-        <v>0.008355880948591438</v>
+        <v>0.00418702023726448</v>
       </c>
       <c r="F339">
-        <v>0.1854480453306093</v>
+        <v>0.06459412320943615</v>
       </c>
       <c r="G339">
         <v>0</v>
       </c>
       <c r="H339">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>(0, 14)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -13605,27 +13605,27 @@
         </is>
       </c>
       <c r="E340">
-        <v>0.003262772560878561</v>
+        <v>0.00418702023726448</v>
       </c>
       <c r="F340">
-        <v>0.08689095412569811</v>
+        <v>0.06459412320943615</v>
       </c>
       <c r="G340">
         <v>0</v>
       </c>
       <c r="H340">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>(0, 6)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -13644,27 +13644,27 @@
         </is>
       </c>
       <c r="E341">
-        <v>0.008674200222823492</v>
+        <v>0.006978367062107467</v>
       </c>
       <c r="F341">
-        <v>0.3243720570131283</v>
+        <v>0.08327369698711283</v>
       </c>
       <c r="G341">
         <v>0</v>
       </c>
       <c r="H341">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13683,10 +13683,10 @@
         </is>
       </c>
       <c r="E342">
-        <v>151162.0879304541</v>
+        <v>147571.3708468468</v>
       </c>
       <c r="F342">
-        <v>309110.0425526967</v>
+        <v>302340.1742073931</v>
       </c>
       <c r="G342">
         <v>0</v>
@@ -13703,7 +13703,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13722,10 +13722,10 @@
         </is>
       </c>
       <c r="E343">
-        <v>223.7341900574907</v>
+        <v>252.7034234234234</v>
       </c>
       <c r="F343">
-        <v>625.2002738285645</v>
+        <v>639.0704224387156</v>
       </c>
       <c r="G343">
         <v>0</v>
@@ -13742,7 +13742,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13761,10 +13761,10 @@
         </is>
       </c>
       <c r="E344">
-        <v>114557.0173531998</v>
+        <v>110934.6837045045</v>
       </c>
       <c r="F344">
-        <v>232712.0924362883</v>
+        <v>227615.0057220722</v>
       </c>
       <c r="G344">
         <v>0</v>
@@ -13781,7 +13781,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13800,27 +13800,27 @@
         </is>
       </c>
       <c r="E345">
-        <v>111.7588573474706</v>
+        <v>161.8427027027027</v>
       </c>
       <c r="F345">
-        <v>156.9167694689064</v>
+        <v>177.3922287633733</v>
       </c>
       <c r="G345">
         <v>1</v>
       </c>
       <c r="H345">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>(1, 1034)</t>
+          <t>(1, 1031)</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13839,10 +13839,10 @@
         </is>
       </c>
       <c r="E346">
-        <v>83.89964113071673</v>
+        <v>120.9012108108108</v>
       </c>
       <c r="F346">
-        <v>122.2207476753129</v>
+        <v>138.5811277168841</v>
       </c>
       <c r="G346">
         <v>0</v>
@@ -13859,7 +13859,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13878,10 +13878,10 @@
         </is>
       </c>
       <c r="E347">
-        <v>10.4661322087171</v>
+        <v>13.06072072072072</v>
       </c>
       <c r="F347">
-        <v>20.10243798281233</v>
+        <v>21.05526773409256</v>
       </c>
       <c r="G347">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13917,10 +13917,10 @@
         </is>
       </c>
       <c r="E348">
-        <v>72.89637748910859</v>
+        <v>107.2046846846847</v>
       </c>
       <c r="F348">
-        <v>106.5005400364544</v>
+        <v>122.7030484994025</v>
       </c>
       <c r="G348">
         <v>0</v>
@@ -13937,7 +13937,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -13956,10 +13956,10 @@
         </is>
       </c>
       <c r="E349">
-        <v>3.584177127056436</v>
+        <v>4.305405405405406</v>
       </c>
       <c r="F349">
-        <v>7.449230106082639</v>
+        <v>7.701932103400988</v>
       </c>
       <c r="G349">
         <v>0</v>
@@ -13976,7 +13976,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="E350">
-        <v>6.689231932204739</v>
+        <v>8.539279279279279</v>
       </c>
       <c r="F350">
-        <v>12.8223419419962</v>
+        <v>13.58752447100487</v>
       </c>
       <c r="G350">
         <v>0</v>
@@ -14015,7 +14015,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14034,27 +14034,27 @@
         </is>
       </c>
       <c r="E351">
-        <v>0.2024110286657781</v>
+        <v>0.2513513513513513</v>
       </c>
       <c r="F351">
-        <v>1.607166624352718</v>
+        <v>1.281047287423756</v>
       </c>
       <c r="G351">
         <v>0</v>
       </c>
       <c r="H351">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 45)</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14073,27 +14073,27 @@
         </is>
       </c>
       <c r="E352">
-        <v>0.06294137540034614</v>
+        <v>0.07153153153153154</v>
       </c>
       <c r="F352">
-        <v>0.5764339251200514</v>
+        <v>0.5073974283479409</v>
       </c>
       <c r="G352">
         <v>0</v>
       </c>
       <c r="H352">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14112,27 +14112,27 @@
         </is>
       </c>
       <c r="E353">
-        <v>0.05794823847699378</v>
+        <v>0.0727927927927928</v>
       </c>
       <c r="F353">
-        <v>0.6211728815818462</v>
+        <v>0.4841312633394754</v>
       </c>
       <c r="G353">
         <v>0</v>
       </c>
       <c r="H353">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14151,27 +14151,27 @@
         </is>
       </c>
       <c r="E354">
-        <v>0.0815214147884382</v>
+        <v>0.107027027027027</v>
       </c>
       <c r="F354">
-        <v>0.6664367378550815</v>
+        <v>0.5733974504136869</v>
       </c>
       <c r="G354">
         <v>0</v>
       </c>
       <c r="H354">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14190,27 +14190,27 @@
         </is>
       </c>
       <c r="E355">
-        <v>0.03787622590463307</v>
+        <v>0.04126126126126126</v>
       </c>
       <c r="F355">
-        <v>0.6037910336824548</v>
+        <v>0.6315931637705925</v>
       </c>
       <c r="G355">
         <v>0</v>
       </c>
       <c r="H355">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14229,27 +14229,27 @@
         </is>
       </c>
       <c r="E356">
-        <v>0.01189599952256858</v>
+        <v>0.01171171171171171</v>
       </c>
       <c r="F356">
-        <v>0.2611744760738401</v>
+        <v>0.2803849845224184</v>
       </c>
       <c r="G356">
         <v>0</v>
       </c>
       <c r="H356">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14268,27 +14268,27 @@
         </is>
       </c>
       <c r="E357">
-        <v>0.01211482225626131</v>
+        <v>0.01675675675675676</v>
       </c>
       <c r="F357">
-        <v>0.2083262307970135</v>
+        <v>0.2945536808453654</v>
       </c>
       <c r="G357">
         <v>0</v>
       </c>
       <c r="H357">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 17)</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>intensive_baseline</t>
+          <t>extensive_baseline_strong</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -14307,27 +14307,27 @@
         </is>
       </c>
       <c r="E358">
-        <v>0.01386540412580318</v>
+        <v>0.01279279279279279</v>
       </c>
       <c r="F358">
-        <v>0.2507780450142128</v>
+        <v>0.1973384407842458</v>
       </c>
       <c r="G358">
         <v>0</v>
       </c>
       <c r="H358">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -14346,10 +14346,10 @@
         </is>
       </c>
       <c r="E359">
-        <v>120096.0426431718</v>
+        <v>122025.6116065035</v>
       </c>
       <c r="F359">
-        <v>250605.7676624816</v>
+        <v>263020.7700876168</v>
       </c>
       <c r="G359">
         <v>0</v>
@@ -14366,7 +14366,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -14385,10 +14385,10 @@
         </is>
       </c>
       <c r="E360">
-        <v>46.87453744493392</v>
+        <v>26.62902156327083</v>
       </c>
       <c r="F360">
-        <v>134.2629973679432</v>
+        <v>104.4420895756076</v>
       </c>
       <c r="G360">
         <v>0</v>
@@ -14405,7 +14405,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14424,10 +14424,10 @@
         </is>
       </c>
       <c r="E361">
-        <v>114576.8312916299</v>
+        <v>115348.880936265</v>
       </c>
       <c r="F361">
-        <v>227822.6291960797</v>
+        <v>235396.665709708</v>
       </c>
       <c r="G361">
         <v>0</v>
@@ -14444,7 +14444,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="E362">
-        <v>150.8664317180617</v>
+        <v>100.1684481341007</v>
       </c>
       <c r="F362">
-        <v>165.1595082259186</v>
+        <v>141.9602120241412</v>
       </c>
       <c r="G362">
         <v>1</v>
@@ -14483,7 +14483,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14502,27 +14502,27 @@
         </is>
       </c>
       <c r="E363">
-        <v>114.9832599118943</v>
+        <v>77.06028697981593</v>
       </c>
       <c r="F363">
-        <v>132.1340187423531</v>
+        <v>113.5625546613916</v>
       </c>
       <c r="G363">
         <v>0</v>
       </c>
       <c r="H363">
-        <v>635</v>
+        <v>653</v>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>(0, 635)</t>
+          <t>(0, 653)</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14541,10 +14541,10 @@
         </is>
       </c>
       <c r="E364">
-        <v>12.98625550660793</v>
+        <v>9.73323077739172</v>
       </c>
       <c r="F364">
-        <v>20.86403323814816</v>
+        <v>18.99030715458966</v>
       </c>
       <c r="G364">
         <v>0</v>
@@ -14561,7 +14561,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14580,27 +14580,27 @@
         </is>
       </c>
       <c r="E365">
-        <v>101.3087224669603</v>
+        <v>66.8974352173567</v>
       </c>
       <c r="F365">
-        <v>116.5173465827175</v>
+        <v>99.25385502892921</v>
       </c>
       <c r="G365">
         <v>0</v>
       </c>
       <c r="H365">
-        <v>617</v>
+        <v>631</v>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>(0, 617)</t>
+          <t>(0, 631)</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14619,10 +14619,10 @@
         </is>
       </c>
       <c r="E366">
-        <v>4.4015859030837</v>
+        <v>3.404901466726786</v>
       </c>
       <c r="F366">
-        <v>7.792241761875399</v>
+        <v>7.192508831064703</v>
       </c>
       <c r="G366">
         <v>0</v>
@@ -14639,7 +14639,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -14658,10 +14658,10 @@
         </is>
       </c>
       <c r="E367">
-        <v>8.390308370044053</v>
+        <v>6.152826035063523</v>
       </c>
       <c r="F367">
-        <v>13.38206799835682</v>
+        <v>12.00801570426784</v>
       </c>
       <c r="G367">
         <v>0</v>
@@ -14678,7 +14678,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -14697,27 +14697,27 @@
         </is>
       </c>
       <c r="E368">
-        <v>0.2544493392070484</v>
+        <v>0.2046521496963107</v>
       </c>
       <c r="F368">
-        <v>1.401732094473962</v>
+        <v>1.685758890151864</v>
       </c>
       <c r="G368">
         <v>0</v>
       </c>
       <c r="H368">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>(0, 45)</t>
+          <t>(0, 173)</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14736,27 +14736,27 @@
         </is>
       </c>
       <c r="E369">
-        <v>0.07718061674008811</v>
+        <v>0.06514070498368831</v>
       </c>
       <c r="F369">
-        <v>0.5330452827903865</v>
+        <v>0.5846246354430156</v>
       </c>
       <c r="G369">
         <v>0</v>
       </c>
       <c r="H369">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14775,27 +14775,27 @@
         </is>
       </c>
       <c r="E370">
-        <v>0.07947136563876651</v>
+        <v>0.06285971938572528</v>
       </c>
       <c r="F370">
-        <v>0.5278895027590327</v>
+        <v>0.6922087080290286</v>
       </c>
       <c r="G370">
         <v>0</v>
       </c>
       <c r="H370">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 98)</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -14814,27 +14814,27 @@
         </is>
       </c>
       <c r="E371">
-        <v>0.09779735682819383</v>
+        <v>0.07665172532689707</v>
       </c>
       <c r="F371">
-        <v>0.6081809884622227</v>
+        <v>0.6438784865424627</v>
       </c>
       <c r="G371">
         <v>0</v>
       </c>
       <c r="H371">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 42)</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14853,27 +14853,27 @@
         </is>
       </c>
       <c r="E372">
-        <v>0.05356828193832599</v>
+        <v>0.04373657268652362</v>
       </c>
       <c r="F372">
-        <v>0.7163574539387912</v>
+        <v>0.622140232443614</v>
       </c>
       <c r="G372">
         <v>0</v>
       </c>
       <c r="H372">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 48)</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14892,27 +14892,27 @@
         </is>
       </c>
       <c r="E373">
-        <v>0.01515418502202643</v>
+        <v>0.01307588255576479</v>
       </c>
       <c r="F373">
-        <v>0.3011834079163516</v>
+        <v>0.2819219105705569</v>
       </c>
       <c r="G373">
         <v>0</v>
       </c>
       <c r="H373">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 33)</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14931,27 +14931,27 @@
         </is>
       </c>
       <c r="E374">
-        <v>0.02185022026431718</v>
+        <v>0.01506511418189534</v>
       </c>
       <c r="F374">
-        <v>0.3346120214739968</v>
+        <v>0.2351889802489741</v>
       </c>
       <c r="G374">
         <v>0</v>
       </c>
       <c r="H374">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>(0, 17)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14970,27 +14970,27 @@
         </is>
       </c>
       <c r="E375">
-        <v>0.01656387665198238</v>
+        <v>0.01559557594886348</v>
       </c>
       <c r="F375">
-        <v>0.2215253763119327</v>
+        <v>0.2208455090834819</v>
       </c>
       <c r="G375">
         <v>0</v>
       </c>
       <c r="H375">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>(0, 10)</t>
+          <t>(0, 14)</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15009,10 +15009,10 @@
         </is>
       </c>
       <c r="E376">
-        <v>232637.4744680851</v>
+        <v>238583.1102798026</v>
       </c>
       <c r="F376">
-        <v>397304.1654732611</v>
+        <v>405571.4550739584</v>
       </c>
       <c r="G376">
         <v>0</v>
@@ -15029,7 +15029,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15048,10 +15048,10 @@
         </is>
       </c>
       <c r="E377">
-        <v>832.8291614518148</v>
+        <v>815.1281235078784</v>
       </c>
       <c r="F377">
-        <v>1029.022950746412</v>
+        <v>1031.828072407631</v>
       </c>
       <c r="G377">
         <v>0</v>
@@ -15068,7 +15068,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15087,10 +15087,10 @@
         </is>
       </c>
       <c r="E378">
-        <v>109836.1096370463</v>
+        <v>112181.1115222028</v>
       </c>
       <c r="F378">
-        <v>224438.7816529119</v>
+        <v>224457.0875408288</v>
       </c>
       <c r="G378">
         <v>0</v>
@@ -15107,7 +15107,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -15126,27 +15126,27 @@
         </is>
       </c>
       <c r="E379">
-        <v>190.3642052565707</v>
+        <v>146.5346968008913</v>
       </c>
       <c r="F379">
-        <v>201.6175198635532</v>
+        <v>190.85408354944</v>
       </c>
       <c r="G379">
         <v>1</v>
       </c>
       <c r="H379">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>(1, 1031)</t>
+          <t>(1, 1034)</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15165,10 +15165,10 @@
         </is>
       </c>
       <c r="E380">
-        <v>136.1975719649562</v>
+        <v>104.4204249562311</v>
       </c>
       <c r="F380">
-        <v>149.9291153359134</v>
+        <v>143.1890819091348</v>
       </c>
       <c r="G380">
         <v>0</v>
@@ -15185,7 +15185,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15204,10 +15204,10 @@
         </is>
       </c>
       <c r="E381">
-        <v>14.91614518147685</v>
+        <v>12.66512812350788</v>
       </c>
       <c r="F381">
-        <v>22.7231681132058</v>
+        <v>22.98141407071184</v>
       </c>
       <c r="G381">
         <v>0</v>
@@ -15224,7 +15224,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15243,10 +15243,10 @@
         </is>
       </c>
       <c r="E382">
-        <v>120.6063829787234</v>
+        <v>90.89559127805188</v>
       </c>
       <c r="F382">
-        <v>131.6761349591464</v>
+        <v>124.0372038381766</v>
       </c>
       <c r="G382">
         <v>0</v>
@@ -15263,7 +15263,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="E383">
-        <v>4.44180225281602</v>
+        <v>4.122075441667993</v>
       </c>
       <c r="F383">
-        <v>7.733592023854689</v>
+        <v>8.147900333619466</v>
       </c>
       <c r="G383">
         <v>0</v>
@@ -15302,7 +15302,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15321,10 +15321,10 @@
         </is>
       </c>
       <c r="E384">
-        <v>10.270337922403</v>
+        <v>8.298663059048225</v>
       </c>
       <c r="F384">
-        <v>15.14313287924839</v>
+        <v>14.88767899561893</v>
       </c>
       <c r="G384">
         <v>0</v>
@@ -15341,7 +15341,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15360,27 +15360,27 @@
         </is>
       </c>
       <c r="E385">
-        <v>0.2365456821026283</v>
+        <v>0.1956867738341557</v>
       </c>
       <c r="F385">
-        <v>0.6008685699053219</v>
+        <v>1.344094575787843</v>
       </c>
       <c r="G385">
         <v>0</v>
       </c>
       <c r="H385">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>(0, 6)</t>
+          <t>(0, 104)</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15399,27 +15399,27 @@
         </is>
       </c>
       <c r="E386">
-        <v>0.05256570713391739</v>
+        <v>0.05634251153907369</v>
       </c>
       <c r="F386">
-        <v>0.2522093739654852</v>
+        <v>0.5510984221513963</v>
       </c>
       <c r="G386">
         <v>0</v>
       </c>
       <c r="H386">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15438,27 +15438,27 @@
         </is>
       </c>
       <c r="E387">
-        <v>0.05757196495619524</v>
+        <v>0.04321184147700143</v>
       </c>
       <c r="F387">
-        <v>0.2680005271352843</v>
+        <v>0.3250438116820141</v>
       </c>
       <c r="G387">
         <v>0</v>
       </c>
       <c r="H387">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15477,27 +15477,27 @@
         </is>
       </c>
       <c r="E388">
-        <v>0.1264080100125156</v>
+        <v>0.09613242081808053</v>
       </c>
       <c r="F388">
-        <v>0.3864207105556317</v>
+        <v>0.7297810254164189</v>
       </c>
       <c r="G388">
         <v>0</v>
       </c>
       <c r="H388">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>(0, 3)</t>
+          <t>(0, 68)</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15516,27 +15516,27 @@
         </is>
       </c>
       <c r="E389">
-        <v>0.01501877346683354</v>
+        <v>0.02029285373229349</v>
       </c>
       <c r="F389">
-        <v>0.1315567152999456</v>
+        <v>0.5446863985501021</v>
       </c>
       <c r="G389">
         <v>0</v>
       </c>
       <c r="H389">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>(0, 2)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15555,27 +15555,27 @@
         </is>
       </c>
       <c r="E390">
-        <v>0.004380475594493116</v>
+        <v>0.008355880948591438</v>
       </c>
       <c r="F390">
-        <v>0.06606071414188501</v>
+        <v>0.1854480453306093</v>
       </c>
       <c r="G390">
         <v>0</v>
       </c>
       <c r="H390">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 14)</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15594,27 +15594,27 @@
         </is>
       </c>
       <c r="E391">
-        <v>0.003754693366708385</v>
+        <v>0.003262772560878561</v>
       </c>
       <c r="F391">
-        <v>0.06117955466046801</v>
+        <v>0.08689095412569811</v>
       </c>
       <c r="G391">
         <v>0</v>
       </c>
       <c r="H391">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 6)</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15633,27 +15633,27 @@
         </is>
       </c>
       <c r="E392">
-        <v>0.00688360450563204</v>
+        <v>0.008674200222823492</v>
       </c>
       <c r="F392">
-        <v>0.08270732227980988</v>
+        <v>0.3243720570131283</v>
       </c>
       <c r="G392">
         <v>0</v>
       </c>
       <c r="H392">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 34)</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15672,10 +15672,10 @@
         </is>
       </c>
       <c r="E393">
-        <v>144823.2814794445</v>
+        <v>151162.0879304541</v>
       </c>
       <c r="F393">
-        <v>292983.980278638</v>
+        <v>309110.0425526967</v>
       </c>
       <c r="G393">
         <v>0</v>
@@ -15692,7 +15692,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15711,10 +15711,10 @@
         </is>
       </c>
       <c r="E394">
-        <v>219.5619414271965</v>
+        <v>223.7341900574907</v>
       </c>
       <c r="F394">
-        <v>593.738354450717</v>
+        <v>625.2002738285645</v>
       </c>
       <c r="G394">
         <v>0</v>
@@ -15731,7 +15731,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15750,10 +15750,10 @@
         </is>
       </c>
       <c r="E395">
-        <v>113535.2152866767</v>
+        <v>114557.0173531998</v>
       </c>
       <c r="F395">
-        <v>227076.5946171218</v>
+        <v>232712.0924362883</v>
       </c>
       <c r="G395">
         <v>0</v>
@@ -15770,7 +15770,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15789,27 +15789,27 @@
         </is>
       </c>
       <c r="E396">
-        <v>159.5447545717035</v>
+        <v>111.7588573474706</v>
       </c>
       <c r="F396">
-        <v>174.5795497996516</v>
+        <v>156.9167694689064</v>
       </c>
       <c r="G396">
         <v>1</v>
       </c>
       <c r="H396">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>(1, 1031)</t>
+          <t>(1, 1034)</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15828,10 +15828,10 @@
         </is>
       </c>
       <c r="E397">
-        <v>119.6443998350062</v>
+        <v>83.89964113071673</v>
       </c>
       <c r="F397">
-        <v>136.5154202724657</v>
+        <v>122.2207476753129</v>
       </c>
       <c r="G397">
         <v>0</v>
@@ -15848,7 +15848,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -15867,10 +15867,10 @@
         </is>
       </c>
       <c r="E398">
-        <v>13.41028461432696</v>
+        <v>10.4661322087171</v>
       </c>
       <c r="F398">
-        <v>21.29982578521687</v>
+        <v>20.10243798281233</v>
       </c>
       <c r="G398">
         <v>0</v>
@@ -15887,7 +15887,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15906,10 +15906,10 @@
         </is>
       </c>
       <c r="E399">
-        <v>105.5487419221779</v>
+        <v>72.89637748910859</v>
       </c>
       <c r="F399">
-        <v>120.2685246035386</v>
+        <v>106.5005400364544</v>
       </c>
       <c r="G399">
         <v>0</v>
@@ -15926,7 +15926,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15945,10 +15945,10 @@
         </is>
       </c>
       <c r="E400">
-        <v>4.410422109170906</v>
+        <v>3.584177127056436</v>
       </c>
       <c r="F400">
-        <v>7.778880766161967</v>
+        <v>7.449230106082639</v>
       </c>
       <c r="G400">
         <v>0</v>
@@ -15965,7 +15965,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15984,10 +15984,10 @@
         </is>
       </c>
       <c r="E401">
-        <v>8.803382373161007</v>
+        <v>6.689231932204739</v>
       </c>
       <c r="F401">
-        <v>13.80917030011436</v>
+        <v>12.8223419419962</v>
       </c>
       <c r="G401">
         <v>0</v>
@@ -16004,7 +16004,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -16023,27 +16023,27 @@
         </is>
       </c>
       <c r="E402">
-        <v>0.2505156056647876</v>
+        <v>0.2024110286657781</v>
       </c>
       <c r="F402">
-        <v>1.269813301423826</v>
+        <v>1.607166624352718</v>
       </c>
       <c r="G402">
         <v>0</v>
       </c>
       <c r="H402">
-        <v>45</v>
+        <v>173</v>
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>(0, 45)</t>
+          <t>(0, 173)</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -16062,27 +16062,27 @@
         </is>
       </c>
       <c r="E403">
-        <v>0.07177230853842981</v>
+        <v>0.06294137540034614</v>
       </c>
       <c r="F403">
-        <v>0.4855637133957096</v>
+        <v>0.5764339251200514</v>
       </c>
       <c r="G403">
         <v>0</v>
       </c>
       <c r="H403">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -16101,27 +16101,27 @@
         </is>
       </c>
       <c r="E404">
-        <v>0.07465970026124021</v>
+        <v>0.05794823847699378</v>
       </c>
       <c r="F404">
-        <v>0.4829974625027792</v>
+        <v>0.6211728815818462</v>
       </c>
       <c r="G404">
         <v>0</v>
       </c>
       <c r="H404">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 98)</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -16140,27 +16140,27 @@
         </is>
       </c>
       <c r="E405">
-        <v>0.1040835968651176</v>
+        <v>0.0815214147884382</v>
       </c>
       <c r="F405">
-        <v>0.5670413143647662</v>
+        <v>0.6664367378550815</v>
       </c>
       <c r="G405">
         <v>0</v>
       </c>
       <c r="H405">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 68)</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -16179,27 +16179,27 @@
         </is>
       </c>
       <c r="E406">
-        <v>0.0450983088134195</v>
+        <v>0.03787622590463307</v>
       </c>
       <c r="F406">
-        <v>0.6359689551571736</v>
+        <v>0.6037910336824548</v>
       </c>
       <c r="G406">
         <v>0</v>
       </c>
       <c r="H406">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>(0, 36)</t>
+          <t>(0, 54)</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -16218,27 +16218,27 @@
         </is>
       </c>
       <c r="E407">
-        <v>0.01278702048673175</v>
+        <v>0.01189599952256858</v>
       </c>
       <c r="F407">
-        <v>0.2678734059060083</v>
+        <v>0.2611744760738401</v>
       </c>
       <c r="G407">
         <v>0</v>
       </c>
       <c r="H407">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>(0, 19)</t>
+          <t>(0, 33)</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -16257,27 +16257,27 @@
         </is>
       </c>
       <c r="E408">
-        <v>0.01787432971263577</v>
+        <v>0.01211482225626131</v>
       </c>
       <c r="F408">
-        <v>0.2970510398709546</v>
+        <v>0.2083262307970135</v>
       </c>
       <c r="G408">
         <v>0</v>
       </c>
       <c r="H408">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>(0, 17)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>intensive_baseline_strong</t>
+          <t>intensive_baseline</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -16296,27 +16296,27 @@
         </is>
       </c>
       <c r="E409">
-        <v>0.01443695861405197</v>
+        <v>0.01386540412580318</v>
       </c>
       <c r="F409">
-        <v>0.1995195409345438</v>
+        <v>0.2507780450142128</v>
       </c>
       <c r="G409">
         <v>0</v>
       </c>
       <c r="H409">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>(0, 10)</t>
+          <t>(0, 34)</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -16335,10 +16335,10 @@
         </is>
       </c>
       <c r="E410">
-        <v>128376.3883411814</v>
+        <v>120096.0426431718</v>
       </c>
       <c r="F410">
-        <v>270808.6390062838</v>
+        <v>250605.7676624816</v>
       </c>
       <c r="G410">
         <v>0</v>
@@ -16355,7 +16355,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -16374,10 +16374,10 @@
         </is>
       </c>
       <c r="E411">
-        <v>27.06159225924381</v>
+        <v>46.87453744493392</v>
       </c>
       <c r="F411">
-        <v>105.5974945612804</v>
+        <v>134.2629973679432</v>
       </c>
       <c r="G411">
         <v>0</v>
@@ -16394,7 +16394,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -16413,10 +16413,10 @@
         </is>
       </c>
       <c r="E412">
-        <v>121188.0128139715</v>
+        <v>114576.8312916299</v>
       </c>
       <c r="F412">
-        <v>241914.6734586206</v>
+        <v>227822.6291960797</v>
       </c>
       <c r="G412">
         <v>0</v>
@@ -16433,7 +16433,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -16452,10 +16452,10 @@
         </is>
       </c>
       <c r="E413">
-        <v>104.0649698992669</v>
+        <v>150.8664317180617</v>
       </c>
       <c r="F413">
-        <v>144.1594262812623</v>
+        <v>165.1595082259186</v>
       </c>
       <c r="G413">
         <v>1</v>
@@ -16472,7 +16472,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -16491,27 +16491,27 @@
         </is>
       </c>
       <c r="E414">
-        <v>78.72804037273251</v>
+        <v>114.9832599118943</v>
       </c>
       <c r="F414">
-        <v>113.3653549541781</v>
+        <v>132.1340187423531</v>
       </c>
       <c r="G414">
         <v>0</v>
       </c>
       <c r="H414">
-        <v>663</v>
+        <v>635</v>
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>(0, 663)</t>
+          <t>(0, 635)</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -16530,10 +16530,10 @@
         </is>
       </c>
       <c r="E415">
-        <v>10.41022431503447</v>
+        <v>12.98625550660793</v>
       </c>
       <c r="F415">
-        <v>19.83772188503681</v>
+        <v>20.86403323814816</v>
       </c>
       <c r="G415">
         <v>0</v>
@@ -16550,7 +16550,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -16569,27 +16569,27 @@
         </is>
       </c>
       <c r="E416">
-        <v>67.84989370368163</v>
+        <v>101.3087224669603</v>
       </c>
       <c r="F416">
-        <v>98.2078968227582</v>
+        <v>116.5173465827175</v>
       </c>
       <c r="G416">
         <v>0</v>
       </c>
       <c r="H416">
-        <v>627</v>
+        <v>617</v>
       </c>
       <c r="I416" t="inlineStr">
         <is>
-          <t>(0, 627)</t>
+          <t>(0, 617)</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -16608,10 +16608,10 @@
         </is>
       </c>
       <c r="E417">
-        <v>3.54815123879915</v>
+        <v>4.4015859030837</v>
       </c>
       <c r="F417">
-        <v>7.393313059426771</v>
+        <v>7.792241761875399</v>
       </c>
       <c r="G417">
         <v>0</v>
@@ -16628,7 +16628,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -16647,10 +16647,10 @@
         </is>
       </c>
       <c r="E418">
-        <v>6.682402495479923</v>
+        <v>8.390308370044053</v>
       </c>
       <c r="F418">
-        <v>12.61490340342768</v>
+        <v>13.38206799835682</v>
       </c>
       <c r="G418">
         <v>0</v>
@@ -16667,7 +16667,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -16686,27 +16686,27 @@
         </is>
       </c>
       <c r="E419">
-        <v>0.2003139218374362</v>
+        <v>0.2544493392070484</v>
       </c>
       <c r="F419">
-        <v>1.657047488366362</v>
+        <v>1.401732094473962</v>
       </c>
       <c r="G419">
         <v>0</v>
       </c>
       <c r="H419">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 45)</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -16725,27 +16725,27 @@
         </is>
       </c>
       <c r="E420">
-        <v>0.05881067334247284</v>
+        <v>0.07718061674008811</v>
       </c>
       <c r="F420">
-        <v>0.534558174589809</v>
+        <v>0.5330452827903865</v>
       </c>
       <c r="G420">
         <v>0</v>
       </c>
       <c r="H420">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>(0, 40)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -16764,27 +16764,27 @@
         </is>
       </c>
       <c r="E421">
-        <v>0.05863185710595856</v>
+        <v>0.07947136563876651</v>
       </c>
       <c r="F421">
-        <v>0.6238835032794365</v>
+        <v>0.5278895027590327</v>
       </c>
       <c r="G421">
         <v>0</v>
       </c>
       <c r="H421">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -16803,27 +16803,27 @@
         </is>
       </c>
       <c r="E422">
-        <v>0.08287139138900479</v>
+        <v>0.09779735682819383</v>
       </c>
       <c r="F422">
-        <v>0.7149359329117667</v>
+        <v>0.6081809884622227</v>
       </c>
       <c r="G422">
         <v>0</v>
       </c>
       <c r="H422">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>(0, 56)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -16842,27 +16842,27 @@
         </is>
       </c>
       <c r="E423">
-        <v>0.03983628380123581</v>
+        <v>0.05356828193832599</v>
       </c>
       <c r="F423">
-        <v>0.5850160307448526</v>
+        <v>0.7163574539387912</v>
       </c>
       <c r="G423">
         <v>0</v>
       </c>
       <c r="H423">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>(0, 48)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -16881,27 +16881,27 @@
         </is>
       </c>
       <c r="E424">
-        <v>0.01055015795434225</v>
+        <v>0.01515418502202643</v>
       </c>
       <c r="F424">
-        <v>0.2272599536902321</v>
+        <v>0.3011834079163516</v>
       </c>
       <c r="G424">
         <v>0</v>
       </c>
       <c r="H424">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16920,27 +16920,27 @@
         </is>
       </c>
       <c r="E425">
-        <v>0.01315292761916115</v>
+        <v>0.02185022026431718</v>
       </c>
       <c r="F425">
-        <v>0.1959906473151492</v>
+        <v>0.3346120214739968</v>
       </c>
       <c r="G425">
         <v>0</v>
       </c>
       <c r="H425">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I425" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 17)</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16959,27 +16959,27 @@
         </is>
       </c>
       <c r="E426">
-        <v>0.01613319822773241</v>
+        <v>0.01656387665198238</v>
       </c>
       <c r="F426">
-        <v>0.2617741909779711</v>
+        <v>0.2215253763119327</v>
       </c>
       <c r="G426">
         <v>0</v>
       </c>
       <c r="H426">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16998,10 +16998,10 @@
         </is>
       </c>
       <c r="E427">
-        <v>217540.4461439774</v>
+        <v>232637.4744680851</v>
       </c>
       <c r="F427">
-        <v>392501.9785230067</v>
+        <v>397304.1654732611</v>
       </c>
       <c r="G427">
         <v>0</v>
@@ -17018,7 +17018,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -17037,10 +17037,10 @@
         </is>
       </c>
       <c r="E428">
-        <v>745.9195896114195</v>
+        <v>832.8291614518148</v>
       </c>
       <c r="F428">
-        <v>1012.560253620886</v>
+        <v>1029.022950746412</v>
       </c>
       <c r="G428">
         <v>0</v>
@@ -17057,7 +17057,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -17076,10 +17076,10 @@
         </is>
       </c>
       <c r="E429">
-        <v>101506.5575752489</v>
+        <v>109836.1096370463</v>
       </c>
       <c r="F429">
-        <v>212726.4883795718</v>
+        <v>224438.7816529119</v>
       </c>
       <c r="G429">
         <v>0</v>
@@ -17096,7 +17096,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -17115,27 +17115,27 @@
         </is>
       </c>
       <c r="E430">
-        <v>131.3797250859106</v>
+        <v>190.3642052565707</v>
       </c>
       <c r="F430">
-        <v>185.4842864036922</v>
+        <v>201.6175198635532</v>
       </c>
       <c r="G430">
         <v>1</v>
       </c>
       <c r="H430">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>(1, 1041)</t>
+          <t>(1, 1031)</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -17154,10 +17154,10 @@
         </is>
       </c>
       <c r="E431">
-        <v>92.17736276323903</v>
+        <v>136.1975719649562</v>
       </c>
       <c r="F431">
-        <v>137.1812591779398</v>
+        <v>149.9291153359134</v>
       </c>
       <c r="G431">
         <v>0</v>
@@ -17174,7 +17174,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -17193,10 +17193,10 @@
         </is>
       </c>
       <c r="E432">
-        <v>11.81319940082827</v>
+        <v>14.91614518147685</v>
       </c>
       <c r="F432">
-        <v>22.69799576093936</v>
+        <v>22.7231681132058</v>
       </c>
       <c r="G432">
         <v>0</v>
@@ -17213,7 +17213,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -17232,10 +17232,10 @@
         </is>
       </c>
       <c r="E433">
-        <v>79.59172614327254</v>
+        <v>120.6063829787234</v>
       </c>
       <c r="F433">
-        <v>117.552640639909</v>
+        <v>131.6761349591464</v>
       </c>
       <c r="G433">
         <v>0</v>
@@ -17252,7 +17252,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -17271,10 +17271,10 @@
         </is>
       </c>
       <c r="E434">
-        <v>3.836020794783682</v>
+        <v>4.44180225281602</v>
       </c>
       <c r="F434">
-        <v>8.067700688278858</v>
+        <v>7.733592023854689</v>
       </c>
       <c r="G434">
         <v>0</v>
@@ -17291,7 +17291,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -17310,10 +17310,10 @@
         </is>
       </c>
       <c r="E435">
-        <v>7.747334566922196</v>
+        <v>10.270337922403</v>
       </c>
       <c r="F435">
-        <v>14.72062901850074</v>
+        <v>15.14313287924839</v>
       </c>
       <c r="G435">
         <v>0</v>
@@ -17330,7 +17330,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -17349,27 +17349,27 @@
         </is>
       </c>
       <c r="E436">
-        <v>0.1477222662789673</v>
+        <v>0.2365456821026283</v>
       </c>
       <c r="F436">
-        <v>0.9772872755999157</v>
+        <v>0.6008685699053219</v>
       </c>
       <c r="G436">
         <v>0</v>
       </c>
       <c r="H436">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="I436" t="inlineStr">
         <is>
-          <t>(0, 104)</t>
+          <t>(0, 6)</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -17388,27 +17388,27 @@
         </is>
       </c>
       <c r="E437">
-        <v>0.04141334038241255</v>
+        <v>0.05256570713391739</v>
       </c>
       <c r="F437">
-        <v>0.3295569902831622</v>
+        <v>0.2522093739654852</v>
       </c>
       <c r="G437">
         <v>0</v>
       </c>
       <c r="H437">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>(0, 22)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -17427,27 +17427,27 @@
         </is>
       </c>
       <c r="E438">
-        <v>0.03722794959908362</v>
+        <v>0.05757196495619524</v>
       </c>
       <c r="F438">
-        <v>0.2438422939269637</v>
+        <v>0.2680005271352843</v>
       </c>
       <c r="G438">
         <v>0</v>
       </c>
       <c r="H438">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>(0, 14)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -17466,27 +17466,27 @@
         </is>
       </c>
       <c r="E439">
-        <v>0.06908097629747115</v>
+        <v>0.1264080100125156</v>
       </c>
       <c r="F439">
-        <v>0.5856849640238003</v>
+        <v>0.3864207105556317</v>
       </c>
       <c r="G439">
         <v>0</v>
       </c>
       <c r="H439">
-        <v>68</v>
+        <v>3</v>
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 3)</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -17505,27 +17505,27 @@
         </is>
       </c>
       <c r="E440">
-        <v>0.01916468411313772</v>
+        <v>0.01501877346683354</v>
       </c>
       <c r="F440">
-        <v>0.4248453900285435</v>
+        <v>0.1315567152999456</v>
       </c>
       <c r="G440">
         <v>0</v>
       </c>
       <c r="H440">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="I440" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 2)</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -17544,27 +17544,27 @@
         </is>
       </c>
       <c r="E441">
-        <v>0.006432284782800247</v>
+        <v>0.004380475594493116</v>
       </c>
       <c r="F441">
-        <v>0.1428350596752989</v>
+        <v>0.06606071414188501</v>
       </c>
       <c r="G441">
         <v>0</v>
       </c>
       <c r="H441">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>(0, 14)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -17583,27 +17583,27 @@
         </is>
       </c>
       <c r="E442">
-        <v>0.003348312626663142</v>
+        <v>0.003754693366708385</v>
       </c>
       <c r="F442">
-        <v>0.07790306155768539</v>
+        <v>0.06117955466046801</v>
       </c>
       <c r="G442">
         <v>0</v>
       </c>
       <c r="H442">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>(0, 6)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -17622,27 +17622,27 @@
         </is>
       </c>
       <c r="E443">
-        <v>0.009384086703674332</v>
+        <v>0.00688360450563204</v>
       </c>
       <c r="F443">
-        <v>0.255442687558208</v>
+        <v>0.08270732227980988</v>
       </c>
       <c r="G443">
         <v>0</v>
       </c>
       <c r="H443">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -17661,10 +17661,10 @@
         </is>
       </c>
       <c r="E444">
-        <v>156089.2939541278</v>
+        <v>144823.2814794445</v>
       </c>
       <c r="F444">
-        <v>316428.7302425733</v>
+        <v>292983.980278638</v>
       </c>
       <c r="G444">
         <v>0</v>
@@ -17681,7 +17681,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -17700,10 +17700,10 @@
         </is>
       </c>
       <c r="E445">
-        <v>250.4884339782826</v>
+        <v>219.5619414271965</v>
       </c>
       <c r="F445">
-        <v>661.085620416169</v>
+        <v>593.738354450717</v>
       </c>
       <c r="G445">
         <v>0</v>
@@ -17720,7 +17720,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -17739,10 +17739,10 @@
         </is>
       </c>
       <c r="E446">
-        <v>115070.8583820537</v>
+        <v>113535.2152866767</v>
       </c>
       <c r="F446">
-        <v>233410.6676878801</v>
+        <v>227076.5946171218</v>
       </c>
       <c r="G446">
         <v>0</v>
@@ -17759,7 +17759,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -17778,27 +17778,27 @@
         </is>
       </c>
       <c r="E447">
-        <v>112.5546152898164</v>
+        <v>159.5447545717035</v>
       </c>
       <c r="F447">
-        <v>158.6673378073866</v>
+        <v>174.5795497996516</v>
       </c>
       <c r="G447">
         <v>1</v>
       </c>
       <c r="H447">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>(1, 1041)</t>
+          <t>(1, 1031)</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -17817,10 +17817,10 @@
         </is>
       </c>
       <c r="E448">
-        <v>82.90819783921455</v>
+        <v>119.6443998350062</v>
       </c>
       <c r="F448">
-        <v>121.428201995975</v>
+        <v>136.5154202724657</v>
       </c>
       <c r="G448">
         <v>0</v>
@@ -17837,7 +17837,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -17856,10 +17856,10 @@
         </is>
       </c>
       <c r="E449">
-        <v>10.84628024483424</v>
+        <v>13.41028461432696</v>
       </c>
       <c r="F449">
-        <v>20.77894117667405</v>
+        <v>21.29982578521687</v>
       </c>
       <c r="G449">
         <v>0</v>
@@ -17876,7 +17876,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -17895,10 +17895,10 @@
         </is>
       </c>
       <c r="E450">
-        <v>71.49934957345712</v>
+        <v>105.5487419221779</v>
       </c>
       <c r="F450">
-        <v>104.744514594377</v>
+        <v>120.2685246035386</v>
       </c>
       <c r="G450">
         <v>0</v>
@@ -17915,7 +17915,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -17934,10 +17934,10 @@
         </is>
       </c>
       <c r="E451">
-        <v>3.637623409878267</v>
+        <v>4.410422109170906</v>
       </c>
       <c r="F451">
-        <v>7.610432945949134</v>
+        <v>7.778880766161967</v>
       </c>
       <c r="G451">
         <v>0</v>
@@ -17954,7 +17954,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -17973,10 +17973,10 @@
         </is>
       </c>
       <c r="E452">
-        <v>7.013391940188145</v>
+        <v>8.803382373161007</v>
       </c>
       <c r="F452">
-        <v>13.31414503855239</v>
+        <v>13.80917030011436</v>
       </c>
       <c r="G452">
         <v>0</v>
@@ -17993,7 +17993,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -18012,27 +18012,27 @@
         </is>
       </c>
       <c r="E453">
-        <v>0.1839680127072807</v>
+        <v>0.2505156056647876</v>
       </c>
       <c r="F453">
-        <v>1.479800408099979</v>
+        <v>1.269813301423826</v>
       </c>
       <c r="G453">
         <v>0</v>
       </c>
       <c r="H453">
-        <v>173</v>
+        <v>45</v>
       </c>
       <c r="I453" t="inlineStr">
         <is>
-          <t>(0, 173)</t>
+          <t>(0, 45)</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -18051,27 +18051,27 @@
         </is>
       </c>
       <c r="E454">
-        <v>0.05340344246806064</v>
+        <v>0.07177230853842981</v>
       </c>
       <c r="F454">
-        <v>0.4803717934628733</v>
+        <v>0.4855637133957096</v>
       </c>
       <c r="G454">
         <v>0</v>
       </c>
       <c r="H454">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>(0, 40)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -18090,27 +18090,27 @@
         </is>
       </c>
       <c r="E455">
-        <v>0.05197935066891235</v>
+        <v>0.07465970026124021</v>
       </c>
       <c r="F455">
-        <v>0.535565954904899</v>
+        <v>0.4829974625027792</v>
       </c>
       <c r="G455">
         <v>0</v>
       </c>
       <c r="H455">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>(0, 98)</t>
+          <t>(0, 22)</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -18129,27 +18129,27 @@
         </is>
       </c>
       <c r="E456">
-        <v>0.07858521957030769</v>
+        <v>0.1040835968651176</v>
       </c>
       <c r="F456">
-        <v>0.6774362394184252</v>
+        <v>0.5670413143647662</v>
       </c>
       <c r="G456">
         <v>0</v>
       </c>
       <c r="H456">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="I456" t="inlineStr">
         <is>
-          <t>(0, 68)</t>
+          <t>(0, 18)</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -18168,27 +18168,27 @@
         </is>
       </c>
       <c r="E457">
-        <v>0.03341138451847896</v>
+        <v>0.0450983088134195</v>
       </c>
       <c r="F457">
-        <v>0.5404247260828672</v>
+        <v>0.6359689551571736</v>
       </c>
       <c r="G457">
         <v>0</v>
       </c>
       <c r="H457">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>(0, 54)</t>
+          <t>(0, 36)</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -18207,27 +18207,27 @@
         </is>
       </c>
       <c r="E458">
-        <v>0.009270289884840268</v>
+        <v>0.01278702048673175</v>
       </c>
       <c r="F458">
-        <v>0.2047902274766143</v>
+        <v>0.2678734059060083</v>
       </c>
       <c r="G458">
         <v>0</v>
       </c>
       <c r="H458">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I458" t="inlineStr">
         <is>
-          <t>(0, 33)</t>
+          <t>(0, 19)</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -18246,27 +18246,27 @@
         </is>
       </c>
       <c r="E459">
-        <v>0.01010557449780224</v>
+        <v>0.01787432971263577</v>
       </c>
       <c r="F459">
-        <v>0.1684639485503475</v>
+        <v>0.2970510398709546</v>
       </c>
       <c r="G459">
         <v>0</v>
       </c>
       <c r="H459">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I459" t="inlineStr">
         <is>
-          <t>(0, 18)</t>
+          <t>(0, 17)</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ads_intensive_baseline</t>
+          <t>intensive_baseline_strong</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -18285,27 +18285,27 @@
         </is>
       </c>
       <c r="E460">
-        <v>0.01403552013583645</v>
+        <v>0.01443695861405197</v>
       </c>
       <c r="F460">
-        <v>0.2598398643505713</v>
+        <v>0.1995195409345438</v>
       </c>
       <c r="G460">
         <v>0</v>
       </c>
       <c r="H460">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>(0, 34)</t>
+          <t>(0, 10)</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>followers_extensive</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -18315,36 +18315,36 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>total_reactions</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>Follows Africa Check</t>
+          <t>Total reactions</t>
         </is>
       </c>
       <c r="E461">
-        <v>0.0283144975088103</v>
+        <v>128376.3883411814</v>
       </c>
       <c r="F461">
-        <v>0.1658723081573669</v>
+        <v>270808.6390062838</v>
       </c>
       <c r="G461">
         <v>0</v>
       </c>
       <c r="H461">
-        <v>1</v>
+        <v>1353335.6</v>
       </c>
       <c r="I461" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1353336)</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>followers_extensive</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -18354,36 +18354,36 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>SMIs</t>
+          <t>total_comments</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>Number of SMIs Followed</t>
+          <t>Total comments</t>
         </is>
       </c>
       <c r="E462">
-        <v>1.01077638990938</v>
+        <v>27.06159225924381</v>
       </c>
       <c r="F462">
-        <v>0.3144757214117411</v>
+        <v>105.5974945612804</v>
       </c>
       <c r="G462">
         <v>0</v>
       </c>
       <c r="H462">
-        <v>9</v>
+        <v>2446</v>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>(0, 9)</t>
+          <t>(0, 2446)</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>followers_extensive_strong</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -18393,36 +18393,36 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>total_shares</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Follows Africa Check</t>
+          <t>Total shares</t>
         </is>
       </c>
       <c r="E463">
-        <v>0.02782071097372488</v>
+        <v>121188.0128139715</v>
       </c>
       <c r="F463">
-        <v>0.1644747562204444</v>
+        <v>241914.6734586206</v>
       </c>
       <c r="G463">
         <v>0</v>
       </c>
       <c r="H463">
-        <v>1</v>
+        <v>1059461.179999999</v>
       </c>
       <c r="I463" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1059461)</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>followers_extensive_strong</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -18432,36 +18432,36 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>SMIs</t>
+          <t>n_posts</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Number of SMIs Followed</t>
+          <t>Number of posts + shares</t>
         </is>
       </c>
       <c r="E464">
-        <v>1.014238346011313</v>
+        <v>104.0649698992669</v>
       </c>
       <c r="F464">
-        <v>0.3346198805275024</v>
+        <v>144.1594262812623</v>
       </c>
       <c r="G464">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H464">
-        <v>6</v>
+        <v>670</v>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>(0, 6)</t>
+          <t>(1, 670)</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>followers_intensive</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -18471,36 +18471,36 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>eng</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>Follows Africa Check</t>
+          <t>Number of posts + shares, English</t>
         </is>
       </c>
       <c r="E465">
-        <v>0.0385645704585842</v>
+        <v>78.72804037273251</v>
       </c>
       <c r="F465">
-        <v>0.1925573363850182</v>
+        <v>113.3653549541781</v>
       </c>
       <c r="G465">
         <v>0</v>
       </c>
       <c r="H465">
-        <v>1</v>
+        <v>663</v>
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 663)</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>followers_intensive</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -18510,36 +18510,36 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>SMIs</t>
+          <t>verifiability</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Number of SMIs Followed</t>
+          <t>Verifiable posts + shares</t>
         </is>
       </c>
       <c r="E466">
-        <v>1.307286364854005</v>
+        <v>10.41022431503447</v>
       </c>
       <c r="F466">
-        <v>0.760755487176385</v>
+        <v>19.83772188503681</v>
       </c>
       <c r="G466">
         <v>0</v>
       </c>
       <c r="H466">
-        <v>9</v>
+        <v>116</v>
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>(0, 9)</t>
+          <t>(0, 116)</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>followers_aggregate</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -18549,36 +18549,36 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>non_ver</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Follows Africa Check</t>
+          <t>Non-verifiable posts + shares</t>
         </is>
       </c>
       <c r="E467">
-        <v>0.0385645704585842</v>
+        <v>67.84989370368163</v>
       </c>
       <c r="F467">
-        <v>0.1925573363850182</v>
+        <v>98.2078968227582</v>
       </c>
       <c r="G467">
         <v>0</v>
       </c>
       <c r="H467">
-        <v>1</v>
+        <v>627</v>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 627)</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>followers_aggregate</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -18588,36 +18588,36 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>SMIs</t>
+          <t>true</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Number of SMIs Followed</t>
+          <t>True posts + shares</t>
         </is>
       </c>
       <c r="E468">
-        <v>1.307286364854005</v>
+        <v>3.54815123879915</v>
       </c>
       <c r="F468">
-        <v>0.760755487176385</v>
+        <v>7.393313059426771</v>
       </c>
       <c r="G468">
         <v>0</v>
       </c>
       <c r="H468">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>(0, 9)</t>
+          <t>(0, 40)</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>followers_ads</t>
+          <t>ads_intensive_baseline</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -18627,66 +18627,2055 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>AC</t>
+          <t>fake</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Follows Africa Check</t>
+          <t>Fake posts + shares</t>
         </is>
       </c>
       <c r="E469">
-        <v>0.05863185710595855</v>
+        <v>6.682402495479923</v>
       </c>
       <c r="F469">
-        <v>0.2349367129327687</v>
+        <v>12.61490340342768</v>
       </c>
       <c r="G469">
         <v>0</v>
       </c>
       <c r="H469">
-        <v>1</v>
+        <v>76</v>
       </c>
       <c r="I469" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 76)</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E470">
+        <v>0.2003139218374362</v>
+      </c>
+      <c r="F470">
+        <v>1.657047488366362</v>
+      </c>
+      <c r="G470">
+        <v>0</v>
+      </c>
+      <c r="H470">
+        <v>173</v>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>(0, 173)</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Positive COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E471">
+        <v>0.05881067334247284</v>
+      </c>
+      <c r="F471">
+        <v>0.534558174589809</v>
+      </c>
+      <c r="G471">
+        <v>0</v>
+      </c>
+      <c r="H471">
+        <v>40</v>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>(0, 40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Neutral COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E472">
+        <v>0.05863185710595856</v>
+      </c>
+      <c r="F472">
+        <v>0.6238835032794365</v>
+      </c>
+      <c r="G472">
+        <v>0</v>
+      </c>
+      <c r="H472">
+        <v>98</v>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>(0, 98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Negative COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E473">
+        <v>0.08287139138900479</v>
+      </c>
+      <c r="F473">
+        <v>0.7149359329117667</v>
+      </c>
+      <c r="G473">
+        <v>0</v>
+      </c>
+      <c r="H473">
+        <v>56</v>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>(0, 56)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E474">
+        <v>0.03983628380123581</v>
+      </c>
+      <c r="F474">
+        <v>0.5850160307448526</v>
+      </c>
+      <c r="G474">
+        <v>0</v>
+      </c>
+      <c r="H474">
+        <v>48</v>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>(0, 48)</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Positive vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E475">
+        <v>0.01055015795434225</v>
+      </c>
+      <c r="F475">
+        <v>0.2272599536902321</v>
+      </c>
+      <c r="G475">
+        <v>0</v>
+      </c>
+      <c r="H475">
+        <v>33</v>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>(0, 33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Neutral vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E476">
+        <v>0.01315292761916115</v>
+      </c>
+      <c r="F476">
+        <v>0.1959906473151492</v>
+      </c>
+      <c r="G476">
+        <v>0</v>
+      </c>
+      <c r="H476">
+        <v>18</v>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>(0, 18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Negative vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E477">
+        <v>0.01613319822773241</v>
+      </c>
+      <c r="F477">
+        <v>0.2617741909779711</v>
+      </c>
+      <c r="G477">
+        <v>0</v>
+      </c>
+      <c r="H477">
+        <v>22</v>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>(0, 22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Total reactions</t>
+        </is>
+      </c>
+      <c r="E478">
+        <v>217540.4461439774</v>
+      </c>
+      <c r="F478">
+        <v>392501.9785230067</v>
+      </c>
+      <c r="G478">
+        <v>0</v>
+      </c>
+      <c r="H478">
+        <v>1353335.6</v>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>(0, 1353336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Total comments</t>
+        </is>
+      </c>
+      <c r="E479">
+        <v>745.9195896114195</v>
+      </c>
+      <c r="F479">
+        <v>1012.560253620886</v>
+      </c>
+      <c r="G479">
+        <v>0</v>
+      </c>
+      <c r="H479">
+        <v>2446</v>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>(0, 2446)</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Total shares</t>
+        </is>
+      </c>
+      <c r="E480">
+        <v>101506.5575752489</v>
+      </c>
+      <c r="F480">
+        <v>212726.4883795718</v>
+      </c>
+      <c r="G480">
+        <v>0</v>
+      </c>
+      <c r="H480">
+        <v>1059461.179999999</v>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>(0, 1059461)</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Number of posts + shares</t>
+        </is>
+      </c>
+      <c r="E481">
+        <v>131.3797250859106</v>
+      </c>
+      <c r="F481">
+        <v>185.4842864036922</v>
+      </c>
+      <c r="G481">
+        <v>1</v>
+      </c>
+      <c r="H481">
+        <v>1041</v>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>(1, 1041)</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Number of posts + shares, English</t>
+        </is>
+      </c>
+      <c r="E482">
+        <v>92.17736276323903</v>
+      </c>
+      <c r="F482">
+        <v>137.1812591779398</v>
+      </c>
+      <c r="G482">
+        <v>0</v>
+      </c>
+      <c r="H482">
+        <v>868.859999999986</v>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>(0, 869)</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Verifiable posts + shares</t>
+        </is>
+      </c>
+      <c r="E483">
+        <v>11.81319940082827</v>
+      </c>
+      <c r="F483">
+        <v>22.69799576093936</v>
+      </c>
+      <c r="G483">
+        <v>0</v>
+      </c>
+      <c r="H483">
+        <v>116</v>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>(0, 116)</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Non-verifiable posts + shares</t>
+        </is>
+      </c>
+      <c r="E484">
+        <v>79.59172614327254</v>
+      </c>
+      <c r="F484">
+        <v>117.552640639909</v>
+      </c>
+      <c r="G484">
+        <v>0</v>
+      </c>
+      <c r="H484">
+        <v>738</v>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>(0, 738)</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>True posts + shares</t>
+        </is>
+      </c>
+      <c r="E485">
+        <v>3.836020794783682</v>
+      </c>
+      <c r="F485">
+        <v>8.067700688278858</v>
+      </c>
+      <c r="G485">
+        <v>0</v>
+      </c>
+      <c r="H485">
+        <v>40</v>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>(0, 40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Fake posts + shares</t>
+        </is>
+      </c>
+      <c r="E486">
+        <v>7.747334566922196</v>
+      </c>
+      <c r="F486">
+        <v>14.72062901850074</v>
+      </c>
+      <c r="G486">
+        <v>0</v>
+      </c>
+      <c r="H486">
+        <v>76</v>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>(0, 76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E487">
+        <v>0.1477222662789673</v>
+      </c>
+      <c r="F487">
+        <v>0.9772872755999157</v>
+      </c>
+      <c r="G487">
+        <v>0</v>
+      </c>
+      <c r="H487">
+        <v>104</v>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>(0, 104)</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Positive COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E488">
+        <v>0.04141334038241255</v>
+      </c>
+      <c r="F488">
+        <v>0.3295569902831622</v>
+      </c>
+      <c r="G488">
+        <v>0</v>
+      </c>
+      <c r="H488">
+        <v>22</v>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>(0, 22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Neutral COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E489">
+        <v>0.03722794959908362</v>
+      </c>
+      <c r="F489">
+        <v>0.2438422939269637</v>
+      </c>
+      <c r="G489">
+        <v>0</v>
+      </c>
+      <c r="H489">
+        <v>14</v>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>(0, 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Negative COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E490">
+        <v>0.06908097629747115</v>
+      </c>
+      <c r="F490">
+        <v>0.5856849640238003</v>
+      </c>
+      <c r="G490">
+        <v>0</v>
+      </c>
+      <c r="H490">
+        <v>68</v>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>(0, 68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E491">
+        <v>0.01916468411313772</v>
+      </c>
+      <c r="F491">
+        <v>0.4248453900285435</v>
+      </c>
+      <c r="G491">
+        <v>0</v>
+      </c>
+      <c r="H491">
+        <v>54</v>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>(0, 54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Positive vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E492">
+        <v>0.006432284782800247</v>
+      </c>
+      <c r="F492">
+        <v>0.1428350596752989</v>
+      </c>
+      <c r="G492">
+        <v>0</v>
+      </c>
+      <c r="H492">
+        <v>14</v>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>(0, 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Neutral vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E493">
+        <v>0.003348312626663142</v>
+      </c>
+      <c r="F493">
+        <v>0.07790306155768539</v>
+      </c>
+      <c r="G493">
+        <v>0</v>
+      </c>
+      <c r="H493">
+        <v>6</v>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>(0, 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>b2</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Negative vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E494">
+        <v>0.009384086703674332</v>
+      </c>
+      <c r="F494">
+        <v>0.255442687558208</v>
+      </c>
+      <c r="G494">
+        <v>0</v>
+      </c>
+      <c r="H494">
+        <v>34</v>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>(0, 34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>total_reactions</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Total reactions</t>
+        </is>
+      </c>
+      <c r="E495">
+        <v>156089.2939541278</v>
+      </c>
+      <c r="F495">
+        <v>316428.7302425733</v>
+      </c>
+      <c r="G495">
+        <v>0</v>
+      </c>
+      <c r="H495">
+        <v>1353335.6</v>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>(0, 1353336)</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>total_comments</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Total comments</t>
+        </is>
+      </c>
+      <c r="E496">
+        <v>250.4884339782826</v>
+      </c>
+      <c r="F496">
+        <v>661.085620416169</v>
+      </c>
+      <c r="G496">
+        <v>0</v>
+      </c>
+      <c r="H496">
+        <v>2446</v>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>(0, 2446)</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>total_shares</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Total shares</t>
+        </is>
+      </c>
+      <c r="E497">
+        <v>115070.8583820537</v>
+      </c>
+      <c r="F497">
+        <v>233410.6676878801</v>
+      </c>
+      <c r="G497">
+        <v>0</v>
+      </c>
+      <c r="H497">
+        <v>1059461.179999999</v>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>(0, 1059461)</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>n_posts</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Number of posts + shares</t>
+        </is>
+      </c>
+      <c r="E498">
+        <v>112.5546152898164</v>
+      </c>
+      <c r="F498">
+        <v>158.6673378073866</v>
+      </c>
+      <c r="G498">
+        <v>1</v>
+      </c>
+      <c r="H498">
+        <v>1041</v>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>(1, 1041)</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>eng</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Number of posts + shares, English</t>
+        </is>
+      </c>
+      <c r="E499">
+        <v>82.90819783921455</v>
+      </c>
+      <c r="F499">
+        <v>121.428201995975</v>
+      </c>
+      <c r="G499">
+        <v>0</v>
+      </c>
+      <c r="H499">
+        <v>868.859999999986</v>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>(0, 869)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>verifiability</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Verifiable posts + shares</t>
+        </is>
+      </c>
+      <c r="E500">
+        <v>10.84628024483424</v>
+      </c>
+      <c r="F500">
+        <v>20.77894117667405</v>
+      </c>
+      <c r="G500">
+        <v>0</v>
+      </c>
+      <c r="H500">
+        <v>116</v>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>(0, 116)</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>non_ver</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Non-verifiable posts + shares</t>
+        </is>
+      </c>
+      <c r="E501">
+        <v>71.49934957345712</v>
+      </c>
+      <c r="F501">
+        <v>104.744514594377</v>
+      </c>
+      <c r="G501">
+        <v>0</v>
+      </c>
+      <c r="H501">
+        <v>738</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>(0, 738)</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>True posts + shares</t>
+        </is>
+      </c>
+      <c r="E502">
+        <v>3.637623409878267</v>
+      </c>
+      <c r="F502">
+        <v>7.610432945949134</v>
+      </c>
+      <c r="G502">
+        <v>0</v>
+      </c>
+      <c r="H502">
+        <v>40</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>(0, 40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>fake</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Fake posts + shares</t>
+        </is>
+      </c>
+      <c r="E503">
+        <v>7.013391940188145</v>
+      </c>
+      <c r="F503">
+        <v>13.31414503855239</v>
+      </c>
+      <c r="G503">
+        <v>0</v>
+      </c>
+      <c r="H503">
+        <v>76</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>(0, 76)</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>n_posts_covid</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E504">
+        <v>0.1839680127072807</v>
+      </c>
+      <c r="F504">
+        <v>1.479800408099979</v>
+      </c>
+      <c r="G504">
+        <v>0</v>
+      </c>
+      <c r="H504">
+        <v>173</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>(0, 173)</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>pos_b_covid</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Positive COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E505">
+        <v>0.05340344246806064</v>
+      </c>
+      <c r="F505">
+        <v>0.4803717934628733</v>
+      </c>
+      <c r="G505">
+        <v>0</v>
+      </c>
+      <c r="H505">
+        <v>40</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>(0, 40)</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>neutral_b_covid</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Neutral COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E506">
+        <v>0.05197935066891235</v>
+      </c>
+      <c r="F506">
+        <v>0.535565954904899</v>
+      </c>
+      <c r="G506">
+        <v>0</v>
+      </c>
+      <c r="H506">
+        <v>98</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>(0, 98)</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>neg_b_covid</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Negative COVID posts + shares</t>
+        </is>
+      </c>
+      <c r="E507">
+        <v>0.07858521957030769</v>
+      </c>
+      <c r="F507">
+        <v>0.6774362394184252</v>
+      </c>
+      <c r="G507">
+        <v>0</v>
+      </c>
+      <c r="H507">
+        <v>68</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>(0, 68)</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>n_posts_vax</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E508">
+        <v>0.03341138451847896</v>
+      </c>
+      <c r="F508">
+        <v>0.5404247260828672</v>
+      </c>
+      <c r="G508">
+        <v>0</v>
+      </c>
+      <c r="H508">
+        <v>54</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>(0, 54)</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>pos_b_vax</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Positive vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E509">
+        <v>0.009270289884840268</v>
+      </c>
+      <c r="F509">
+        <v>0.2047902274766143</v>
+      </c>
+      <c r="G509">
+        <v>0</v>
+      </c>
+      <c r="H509">
+        <v>33</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>(0, 33)</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>neutral_b_vax</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Neutral vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E510">
+        <v>0.01010557449780224</v>
+      </c>
+      <c r="F510">
+        <v>0.1684639485503475</v>
+      </c>
+      <c r="G510">
+        <v>0</v>
+      </c>
+      <c r="H510">
+        <v>18</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>(0, 18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>ads_intensive_baseline</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>both</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>neg_b_vax</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Negative vaccine posts + shares</t>
+        </is>
+      </c>
+      <c r="E511">
+        <v>0.01403552013583645</v>
+      </c>
+      <c r="F511">
+        <v>0.2598398643505713</v>
+      </c>
+      <c r="G511">
+        <v>0</v>
+      </c>
+      <c r="H511">
+        <v>34</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>(0, 34)</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>followers_extensive</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Follows Africa Check</t>
+        </is>
+      </c>
+      <c r="E512">
+        <v>0.0283144975088103</v>
+      </c>
+      <c r="F512">
+        <v>0.1658723081573669</v>
+      </c>
+      <c r="G512">
+        <v>0</v>
+      </c>
+      <c r="H512">
+        <v>1</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>followers_extensive</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>SMIs</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Number of SMIs Followed</t>
+        </is>
+      </c>
+      <c r="E513">
+        <v>1.01077638990938</v>
+      </c>
+      <c r="F513">
+        <v>0.3144757214117411</v>
+      </c>
+      <c r="G513">
+        <v>0</v>
+      </c>
+      <c r="H513">
+        <v>9</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>(0, 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>followers_extensive_strong</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Follows Africa Check</t>
+        </is>
+      </c>
+      <c r="E514">
+        <v>0.02782071097372488</v>
+      </c>
+      <c r="F514">
+        <v>0.1644747562204444</v>
+      </c>
+      <c r="G514">
+        <v>0</v>
+      </c>
+      <c r="H514">
+        <v>1</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>followers_extensive_strong</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>SMIs</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Number of SMIs Followed</t>
+        </is>
+      </c>
+      <c r="E515">
+        <v>1.014238346011313</v>
+      </c>
+      <c r="F515">
+        <v>0.3346198805275024</v>
+      </c>
+      <c r="G515">
+        <v>0</v>
+      </c>
+      <c r="H515">
+        <v>6</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>(0, 6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>followers_intensive</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Follows Africa Check</t>
+        </is>
+      </c>
+      <c r="E516">
+        <v>0.0385645704585842</v>
+      </c>
+      <c r="F516">
+        <v>0.1925573363850182</v>
+      </c>
+      <c r="G516">
+        <v>0</v>
+      </c>
+      <c r="H516">
+        <v>1</v>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>followers_intensive</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>SMIs</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Number of SMIs Followed</t>
+        </is>
+      </c>
+      <c r="E517">
+        <v>1.307286364854005</v>
+      </c>
+      <c r="F517">
+        <v>0.760755487176385</v>
+      </c>
+      <c r="G517">
+        <v>0</v>
+      </c>
+      <c r="H517">
+        <v>9</v>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>(0, 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>followers_aggregate</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Follows Africa Check</t>
+        </is>
+      </c>
+      <c r="E518">
+        <v>0.0385645704585842</v>
+      </c>
+      <c r="F518">
+        <v>0.1925573363850182</v>
+      </c>
+      <c r="G518">
+        <v>0</v>
+      </c>
+      <c r="H518">
+        <v>1</v>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>followers_aggregate</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>SMIs</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Number of SMIs Followed</t>
+        </is>
+      </c>
+      <c r="E519">
+        <v>1.307286364854005</v>
+      </c>
+      <c r="F519">
+        <v>0.760755487176385</v>
+      </c>
+      <c r="G519">
+        <v>0</v>
+      </c>
+      <c r="H519">
+        <v>9</v>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>(0, 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
           <t>followers_ads</t>
         </is>
       </c>
-      <c r="B470" t="inlineStr">
+      <c r="B520" t="inlineStr">
         <is>
           <t>b1</t>
         </is>
       </c>
-      <c r="C470" t="inlineStr">
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Follows Africa Check</t>
+        </is>
+      </c>
+      <c r="E520">
+        <v>0.05863185710595855</v>
+      </c>
+      <c r="F520">
+        <v>0.2349367129327687</v>
+      </c>
+      <c r="G520">
+        <v>0</v>
+      </c>
+      <c r="H520">
+        <v>1</v>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>followers_ads</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>b1</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
         <is>
           <t>SMIs</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr">
+      <c r="D521" t="inlineStr">
         <is>
           <t>Number of SMIs Followed</t>
         </is>
       </c>
-      <c r="E470">
+      <c r="E521">
         <v>2.125836377817003</v>
       </c>
-      <c r="F470">
+      <c r="F521">
         <v>1.667869324168561</v>
       </c>
-      <c r="G470">
-        <v>0</v>
-      </c>
-      <c r="H470">
+      <c r="G521">
+        <v>0</v>
+      </c>
+      <c r="H521">
         <v>17</v>
       </c>
-      <c r="I470" t="inlineStr">
+      <c r="I521" t="inlineStr">
         <is>
           <t>(0, 17)</t>
         </is>
